--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_AVAS-CSTD-0-00-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_AVAS-CSTD-0-00-A-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\10_mcu\19epfv3_mcu_app_mainline\src\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01E81FB-48B9-42EC-B65C-E624E67F688F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8F17E7-B50B-4E9D-A1EF-A1F9E4EAB174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7575" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14535" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="12" r:id="rId1"/>
@@ -674,7 +674,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="305">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2638,9 +2638,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>○</t>
-  </si>
-  <si>
     <t>MALFUNC</t>
   </si>
   <si>
@@ -2695,10 +2692,6 @@
   </si>
   <si>
     <t>ON</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VPNW</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3114,9 +3107,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>(株)NTTデータMSE</t>
-  </si>
-  <si>
     <t>承認</t>
     <rPh sb="0" eb="2">
       <t>ショウニン</t>
@@ -3226,6 +3216,35 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>－</t>
+  </si>
+  <si>
+    <t>DTPH Kiko</t>
+  </si>
+  <si>
+    <t>1.0.2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(株)デンソー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BEVシス検ADAS
+課題対応（BEV3CDCMET-2941）
+[Matrix]シート
+・RWの記載を変更（○→ー）
+[CH_Design]シート
+・RWの記載を変更（VPNW→ー）</t>
+    <rPh sb="11" eb="13">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイオウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3588,7 +3607,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="82">
+  <borders count="83">
     <border>
       <left/>
       <right/>
@@ -4647,6 +4666,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -4659,7 +4691,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="313">
+  <cellXfs count="318">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5411,6 +5443,21 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="81" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5885,17 +5932,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>100782</xdr:colOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>3104</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>100782</xdr:rowOff>
+      <xdr:rowOff>88829</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CC6DCBA-E975-76E0-C1FA-0927A85BA736}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{668BA7B6-13A1-FDC9-82AB-B197EEDD4223}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5911,7 +5958,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5490882" y="8157882"/>
+          <a:off x="5000625" y="8420100"/>
           <a:ext cx="571429" cy="571429"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10104,17 +10151,17 @@
       <sheetName val="４．ナビモデル"/>
       <sheetName val="３．サウンドモデル"/>
       <sheetName val="２．ラジオモデル"/>
+      <sheetName val="1.概述"/>
       <sheetName val="V200複合試験_担当分け_(2)1"/>
       <sheetName val="Spec_List_(19MC-DCM)_1"/>
       <sheetName val="Cooling_Unit"/>
-      <sheetName val="1.概述"/>
       <sheetName val="OpenIssueList"/>
-      <sheetName val="PullDown"/>
       <sheetName val="ECU基盤"/>
       <sheetName val="Name2"/>
       <sheetName val="Name3"/>
       <sheetName val="Company"/>
       <sheetName val="Name"/>
+      <sheetName val="PullDown"/>
       <sheetName val="エンジン型式"/>
       <sheetName val="分类数据"/>
       <sheetName val="index"/>
@@ -10146,6 +10193,37 @@
       <sheetName val="改訂履歴"/>
       <sheetName val="Sheet1"/>
       <sheetName val="⑥フューエル"/>
+      <sheetName val="STEP1-Definition"/>
+      <sheetName val="No.31"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="测试计划"/>
+      <sheetName val="2.2.4_起動終了時"/>
+      <sheetName val="全戻りﾊﾞｸﾞ"/>
+      <sheetName val="DataShare"/>
+      <sheetName val="ＯＰＭ設備"/>
+      <sheetName val="償却計算"/>
+      <sheetName val="技術費"/>
+      <sheetName val="消耗材"/>
+      <sheetName val="生産用消耗工具費"/>
+      <sheetName val="投資込みＭＪ原価"/>
+      <sheetName val="ＭＪ加工費"/>
+      <sheetName val="仕損根拠"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="ERRＩＤ90"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="調査シート"/>
+      <sheetName val="SCH"/>
+      <sheetName val="发行控制"/>
+      <sheetName val="Vibrate test"/>
+      <sheetName val="Data"/>
+      <sheetName val="注釈"/>
+      <sheetName val="仕向け決定用情報取得(GM250)"/>
+      <sheetName val="付録①（GM用）"/>
+      <sheetName val="Data.Share"/>
+      <sheetName val="Func.Share"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -10226,10 +10304,10 @@
       <sheetData sheetId="57" refreshError="1"/>
       <sheetData sheetId="58" refreshError="1"/>
       <sheetData sheetId="59" refreshError="1"/>
-      <sheetData sheetId="60"/>
+      <sheetData sheetId="60" refreshError="1"/>
       <sheetData sheetId="61"/>
       <sheetData sheetId="62"/>
-      <sheetData sheetId="63" refreshError="1"/>
+      <sheetData sheetId="63"/>
       <sheetData sheetId="64" refreshError="1"/>
       <sheetData sheetId="65" refreshError="1"/>
       <sheetData sheetId="66" refreshError="1"/>
@@ -10268,6 +10346,37 @@
       <sheetData sheetId="99" refreshError="1"/>
       <sheetData sheetId="100" refreshError="1"/>
       <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10406,12 +10515,49 @@
       <sheetName val="Config - dspmgr"/>
       <sheetName val="凡例・注記記載用"/>
       <sheetName val="入力パラメータ"/>
-      <sheetName val="原紙"/>
       <sheetName val="マスタテーブル登録データ"/>
       <sheetName val="記入シート"/>
+      <sheetName val="原紙"/>
       <sheetName val="format"/>
       <sheetName val="検査シート"/>
       <sheetName val="1.概述"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="集計表"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="Defined Layout Screen_Ver.0.6"/>
+      <sheetName val="ｲﾝﾊﾟｸﾄ影響台数集計表"/>
+      <sheetName val="実勢(売上)台数表"/>
+      <sheetName val="月別企画台数表"/>
+      <sheetName val="プロジェクト一覧表(現行)"/>
+      <sheetName val="限界利益表(半期別)"/>
+      <sheetName val="機種マスタ"/>
+      <sheetName val="機種ﾏｽﾀ（他車）"/>
+      <sheetName val="売上高表(半期別)"/>
+      <sheetName val="地点情報データ応答"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="リソーセス算出"/>
+      <sheetName val="定義"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="変更区分一覧"/>
+      <sheetName val="難易度量一覧"/>
+      <sheetName val="ユーザ一覧"/>
+      <sheetName val="Normal(Mark)"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="入力規則"/>
+      <sheetName val="#REF"/>
+      <sheetName val="Contents"/>
+      <sheetName val="選択肢"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -10484,7 +10630,7 @@
       <sheetData sheetId="61" refreshError="1"/>
       <sheetData sheetId="62" refreshError="1"/>
       <sheetData sheetId="63" refreshError="1"/>
-      <sheetData sheetId="64" refreshError="1"/>
+      <sheetData sheetId="64"/>
       <sheetData sheetId="65" refreshError="1"/>
       <sheetData sheetId="66"/>
       <sheetData sheetId="67"/>
@@ -10499,7 +10645,7 @@
       <sheetData sheetId="76"/>
       <sheetData sheetId="77" refreshError="1"/>
       <sheetData sheetId="78" refreshError="1"/>
-      <sheetData sheetId="79" refreshError="1"/>
+      <sheetData sheetId="79"/>
       <sheetData sheetId="80"/>
       <sheetData sheetId="81" refreshError="1"/>
       <sheetData sheetId="82" refreshError="1"/>
@@ -10555,6 +10701,43 @@
       <sheetData sheetId="132" refreshError="1"/>
       <sheetData sheetId="133" refreshError="1"/>
       <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
+      <sheetData sheetId="141" refreshError="1"/>
+      <sheetData sheetId="142" refreshError="1"/>
+      <sheetData sheetId="143" refreshError="1"/>
+      <sheetData sheetId="144" refreshError="1"/>
+      <sheetData sheetId="145" refreshError="1"/>
+      <sheetData sheetId="146" refreshError="1"/>
+      <sheetData sheetId="147" refreshError="1"/>
+      <sheetData sheetId="148" refreshError="1"/>
+      <sheetData sheetId="149" refreshError="1"/>
+      <sheetData sheetId="150" refreshError="1"/>
+      <sheetData sheetId="151" refreshError="1"/>
+      <sheetData sheetId="152" refreshError="1"/>
+      <sheetData sheetId="153" refreshError="1"/>
+      <sheetData sheetId="154" refreshError="1"/>
+      <sheetData sheetId="155" refreshError="1"/>
+      <sheetData sheetId="156" refreshError="1"/>
+      <sheetData sheetId="157" refreshError="1"/>
+      <sheetData sheetId="158" refreshError="1"/>
+      <sheetData sheetId="159" refreshError="1"/>
+      <sheetData sheetId="160" refreshError="1"/>
+      <sheetData sheetId="161" refreshError="1"/>
+      <sheetData sheetId="162" refreshError="1"/>
+      <sheetData sheetId="163" refreshError="1"/>
+      <sheetData sheetId="164" refreshError="1"/>
+      <sheetData sheetId="165" refreshError="1"/>
+      <sheetData sheetId="166" refreshError="1"/>
+      <sheetData sheetId="167" refreshError="1"/>
+      <sheetData sheetId="168" refreshError="1"/>
+      <sheetData sheetId="169" refreshError="1"/>
+      <sheetData sheetId="170" refreshError="1"/>
+      <sheetData sheetId="171" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10736,10 +10919,10 @@
       <sheetName val="CPF"/>
       <sheetName val="編集"/>
       <sheetName val="PAIData"/>
+      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="NCastalone"/>
       <sheetName val="dongia (2)"/>
       <sheetName val="Volumes"/>
-      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="加工費"/>
       <sheetName val="車両仕様 嗼1嗼1噌1鲌"/>
       <sheetName val="車両仕様 勜+勜+匬+鲌"/>
@@ -10749,8 +10932,8 @@
       <sheetName val="Y230"/>
       <sheetName val="MASTER"/>
       <sheetName val="設定"/>
+      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="⑥フューエル"/>
-      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ"/>
       <sheetName val="設品表01-3-23作成"/>
       <sheetName val="wire"/>
@@ -10766,25 +10949,24 @@
       <sheetName val="610L611L品番一覧"/>
       <sheetName val="【Input】見積基礎情報（海外生産分)"/>
       <sheetName val="IM-P-L-JB "/>
-      <sheetName val="797T輸入部品リスト"/>
-      <sheetName val="テーブル"/>
-      <sheetName val="Master Updated(517)"/>
-      <sheetName val="４-２．151項目累積（日本）"/>
-      <sheetName val="５-２．151項目累積（北米）"/>
-      <sheetName val="５-１．151項目詳細（北米）"/>
-      <sheetName val="545N仕様ﾗﾌ2"/>
-      <sheetName val="商品力向上"/>
-      <sheetName val="OP-PD"/>
-      <sheetName val="６２３Ｔ"/>
+      <sheetName val="RMBSS's Triggered"/>
+      <sheetName val="_"/>
       <sheetName val="Main 2"/>
       <sheetName val="Datasheet from R. Hinds"/>
-      <sheetName val="GMT900 IPC"/>
+      <sheetName val="545N仕様ﾗﾌ2"/>
+      <sheetName val="Master Updated(517)"/>
+      <sheetName val="６２３Ｔ"/>
+      <sheetName val="商品力向上"/>
+      <sheetName val="ED AND EDOV"/>
       <sheetName val="HORAS_TRAB"/>
       <sheetName val="Resumo_Corolla"/>
       <sheetName val="GASTOS_COROLLA"/>
-      <sheetName val="CALC"/>
-      <sheetName val="ﾘｽﾄ候補"/>
-      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="④要素記号一覧表"/>
+      <sheetName val="START"/>
+      <sheetName val="Blue Flag"/>
+      <sheetName val="Calc Sheet Budget"/>
+      <sheetName val="見積一覧（１案）"/>
+      <sheetName val="部品"/>
       <sheetName val="①評価項目_メーカー"/>
       <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0011__x00"/>
       <sheetName val="車両仕様4__x005f_x0000__x005f_x0011__x005f_x0000_"/>
@@ -10811,16 +10993,9 @@
       <sheetName val="車両仕様_4___x005f_x005f_x005f_x005f_x005f_x005f_x001"/>
       <sheetName val="車両仕様4___x005f_x005f_x005f_x005f_x005f_x005f_x0011"/>
       <sheetName val="EFFY_MAZDA"/>
-      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
-      <sheetName val="_"/>
-      <sheetName val="RMBSS's Triggered"/>
-      <sheetName val="ED AND EDOV"/>
-      <sheetName val="④要素記号一覧表"/>
-      <sheetName val="START"/>
-      <sheetName val="Blue Flag"/>
-      <sheetName val="Calc Sheet Budget"/>
-      <sheetName val="見積一覧（１案）"/>
-      <sheetName val="部品"/>
+      <sheetName val="４-２．151項目累積（日本）"/>
+      <sheetName val="５-２．151項目累積（北米）"/>
+      <sheetName val="５-１．151項目詳細（北米）"/>
       <sheetName val="sebelumCR"/>
       <sheetName val="08TMME"/>
       <sheetName val="VCPT"/>
@@ -10830,6 +11005,14 @@
       <sheetName val="WIP Cal Sheet"/>
       <sheetName val="Pricing overview"/>
       <sheetName val="駆動系1"/>
+      <sheetName val="797T輸入部品リスト"/>
+      <sheetName val="テーブル"/>
+      <sheetName val="OP-PD"/>
+      <sheetName val="GMT900 IPC"/>
+      <sheetName val="CALC"/>
+      <sheetName val="ﾘｽﾄ候補"/>
+      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
       <sheetName val="393.N"/>
       <sheetName val="CæÊ _x0015_ Op"/>
       <sheetName val="ƒƒCƒ“‰æ–Ê _x0015_ Op"/>
@@ -10849,6 +11032,10 @@
       <sheetName val="車両仕様_ᵣ逰ᵣ邀ᵣ郰ᵣ"/>
       <sheetName val="他"/>
       <sheetName val="part"/>
+      <sheetName val="415T原"/>
+      <sheetName val="PAC14"/>
+      <sheetName val="部品表"/>
+      <sheetName val="■07中期明細雛形"/>
       <sheetName val="Vectra"/>
       <sheetName val="PRADO"/>
       <sheetName val="Previous"/>
@@ -10888,10 +11075,6 @@
       <sheetName val="OTHERS x620"/>
       <sheetName val="Ref"/>
       <sheetName val="TOTAL P2"/>
-      <sheetName val="415T原"/>
-      <sheetName val="PAC14"/>
-      <sheetName val="部品表"/>
-      <sheetName val="■07中期明細雛形"/>
       <sheetName val="BUYERS"/>
       <sheetName val="Status"/>
       <sheetName val="PR"/>
@@ -11879,18 +12062,18 @@
       <sheetName val="SUM"/>
       <sheetName val="ﾄﾗｯｸ"/>
       <sheetName val="00"/>
+      <sheetName val="追加検討（調光外部出力）"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="option"/>
       <sheetName val="課題管理"/>
       <sheetName val="C-55227AB"/>
       <sheetName val="Data Definition"/>
       <sheetName val="FC_まとめる"/>
-      <sheetName val="vocabulary"/>
-      <sheetName val="Calibration"/>
-      <sheetName val="CVBS"/>
-      <sheetName val="RGB"/>
       <sheetName val="車両仕様_4___x0011__x00"/>
       <sheetName val="ドメインリスト"/>
-      <sheetName val="option"/>
-      <sheetName val="追加検討（調光外部出力）"/>
       <sheetName val="入力規則"/>
       <sheetName val="Inf"/>
       <sheetName val="#REF!"/>
@@ -11981,8 +12164,29 @@
       <sheetName val="入力LIST"/>
       <sheetName val="パラメータ一覧(AXSS.AXCS)"/>
       <sheetName val="設定値定義"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="All"/>
+      <sheetName val="58831-06360"/>
+      <sheetName val="1999.4"/>
+      <sheetName val="車両仕様 _x005f_x0000__x005f_x0000__x005f_x000a__x000"/>
+      <sheetName val="車両仕様_x005f_x0000_ῃ_x005f_x0000__x005f_x0014__x000"/>
+      <sheetName val="車両仕様_x005f_x0000__x005f_x0000__x005f_x0000__x0000"/>
+      <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
+      <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
+      <sheetName val="SHEET  car no"/>
       <sheetName val="車両仕様????帅?"/>
       <sheetName val="Net Price Position _ Sheet 1"/>
+      <sheetName val="Packing_List2"/>
+      <sheetName val="Packing_List"/>
+      <sheetName val="Calculation_PS"/>
+      <sheetName val="Customer_behaver"/>
+      <sheetName val="Seat_Assy_Tool_Tracking"/>
+      <sheetName val="Stock_in_Trade1"/>
+      <sheetName val="Packing_List21"/>
+      <sheetName val="Packing_List1"/>
+      <sheetName val="Calculation_PS1"/>
+      <sheetName val="Customer_behaver1"/>
+      <sheetName val="Seat_Assy_Tool_Tracking1"/>
       <sheetName val="POs"/>
       <sheetName val="計算式"/>
       <sheetName val="工管合計"/>
@@ -13506,15 +13710,9 @@
       <sheetName val="5"/>
       <sheetName val="確認ｼｰﾄ(TBU)"/>
       <sheetName val="Sheet1 (2)"/>
-      <sheetName val="SHEET  car no"/>
       <sheetName val="サイクル"/>
       <sheetName val="特殊サイクル一覧"/>
       <sheetName val="カメラ"/>
-      <sheetName val="車両仕様 _x005f_x0000__x005f_x0000__x005f_x000a__x000"/>
-      <sheetName val="車両仕様_x005f_x0000_ῃ_x005f_x0000__x005f_x0014__x000"/>
-      <sheetName val="車両仕様_x005f_x0000__x005f_x0000__x005f_x0000__x0000"/>
-      <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
-      <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
       <sheetName val="台数"/>
       <sheetName val="MET397D-25"/>
       <sheetName val="集計表"/>
@@ -13523,21 +13721,6 @@
       <sheetName val="Ｓｉ問連"/>
       <sheetName val="アップロード系(2)"/>
       <sheetName val="エンジン型式"/>
-      <sheetName val="リストデータ"/>
-      <sheetName val="All"/>
-      <sheetName val="58831-06360"/>
-      <sheetName val="1999.4"/>
-      <sheetName val="Packing_List2"/>
-      <sheetName val="Packing_List"/>
-      <sheetName val="Calculation_PS"/>
-      <sheetName val="Customer_behaver"/>
-      <sheetName val="Seat_Assy_Tool_Tracking"/>
-      <sheetName val="Stock_in_Trade1"/>
-      <sheetName val="Packing_List21"/>
-      <sheetName val="Packing_List1"/>
-      <sheetName val="Calculation_PS1"/>
-      <sheetName val="Customer_behaver1"/>
-      <sheetName val="Seat_Assy_Tool_Tracking1"/>
       <sheetName val="Index"/>
       <sheetName val="Defined Layout Screen_Ver.0.6"/>
       <sheetName val="９ｘ"/>
@@ -13549,6 +13732,185 @@
       <sheetName val="config"/>
       <sheetName val="地点情報データ応答"/>
       <sheetName val="Par"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="ETC機能判定"/>
+      <sheetName val="ETCメニュー"/>
+      <sheetName val="登録情報表示"/>
+      <sheetName val="ETC設定"/>
+      <sheetName val="履歴情報表示"/>
+      <sheetName val="履歴情報詳細表示"/>
+      <sheetName val="メニュー２"/>
+      <sheetName val="割込み(Disp)"/>
+      <sheetName val="割込み(Navi)"/>
+      <sheetName val="走行強制状態変化"/>
+      <sheetName val="入力パラメータ"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="リスト画面"/>
+      <sheetName val="特殊画面"/>
+      <sheetName val="入力画面"/>
+      <sheetName val="メッセージ受信開始"/>
+      <sheetName val="Mark"/>
+      <sheetName val="Contents"/>
+      <sheetName val="車両仕様4_ "/>
+      <sheetName val="改正履歴"/>
+      <sheetName val="リスト選択用"/>
+      <sheetName val="变更履历"/>
+      <sheetName val="Menu List"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="検査シート"/>
+      <sheetName val="Cover"/>
+      <sheetName val="MIS REPORT "/>
+      <sheetName val="（別紙5-1）PP02簡素化"/>
+      <sheetName val="universal"/>
+      <sheetName val="Cost Casting"/>
+      <sheetName val="paint mtrl"/>
+      <sheetName val="corolla_095W_"/>
+      <sheetName val="dyna"/>
+      <sheetName val="FC"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="ﾕｰｻﾞｰ設定"/>
+      <sheetName val="同行评审"/>
+      <sheetName val="5.心配点抽出-0"/>
+      <sheetName val="0.表紙"/>
+      <sheetName val="1._概要"/>
+      <sheetName val="4 選局"/>
+      <sheetName val="定数"/>
+      <sheetName val="Case 21_1"/>
+      <sheetName val="96期(川崎)"/>
+      <sheetName val="ORDSHP"/>
+      <sheetName val="B"/>
+      <sheetName val="Blue_Flag3"/>
+      <sheetName val="Calc_Sheet_Budget3"/>
+      <sheetName val="_PART_479W_LHD3"/>
+      <sheetName val="_PART_MYY5A3"/>
+      <sheetName val="393_N3"/>
+      <sheetName val="WIP_Cal_Sheet3"/>
+      <sheetName val="Pricing_overview3"/>
+      <sheetName val="Lookup_Table3"/>
+      <sheetName val="promo_lists_20113"/>
+      <sheetName val="車両仕様_嗼1嗼1噌1鲌3"/>
+      <sheetName val="車両仕様_勜+勜+匬+鲌3"/>
+      <sheetName val="EquipmentTrimming_Cabin_NS3"/>
+      <sheetName val="Reference_3"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000_?_x005f_x0012_?瞳?3"/>
+      <sheetName val="車両仕様_???_x005f_x0012_?瞳?3"/>
+      <sheetName val="160th_NPCC_Nov'103"/>
+      <sheetName val="RMBSS's_Triggered3"/>
+      <sheetName val="車両仕様?4???_??3"/>
+      <sheetName val="車両仕様_???_?瞳?3"/>
+      <sheetName val="車両仕様???ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様?4??_?3"/>
+      <sheetName val="車両仕様4??_?3"/>
+      <sheetName val="車両仕様____瞳_3"/>
+      <sheetName val="車両仕様______瞳_3"/>
+      <sheetName val="車両仕様_4______3"/>
+      <sheetName val="車両仕様___ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様_4____3"/>
+      <sheetName val="車両仕様4____3"/>
+      <sheetName val="PRICE_LIST3"/>
+      <sheetName val="Loss_Time3"/>
+      <sheetName val="Price_range_IT3"/>
+      <sheetName val="Avensis+d_seg__in_&amp;_out_of_UK+3"/>
+      <sheetName val="#ofclose__xl3"/>
+      <sheetName val="Annexes_toutes_bases3"/>
+      <sheetName val="DON_GIA3"/>
+      <sheetName val="CHITIET_VL-NC3"/>
+      <sheetName val="TONGKE3p_3"/>
+      <sheetName val="TOTAL_P23"/>
+      <sheetName val="2_-_Summary3"/>
+      <sheetName val="IPOTESI_PIANO_STATICA3"/>
+      <sheetName val="make_up3"/>
+      <sheetName val="車両仕様_???_x005f_x005f_x005f_x0012_?瞳?3"/>
+      <sheetName val="調達担当者(06_2～)3"/>
+      <sheetName val="車両仕様__x005f_x0000__2"/>
+      <sheetName val="車両仕様_x005f_x0000__N2"/>
+      <sheetName val="車両仕様___x005f_x0012_2"/>
+      <sheetName val="車両仕様__x005f_x005f_x2"/>
+      <sheetName val="車両仕様___x005f_x005f_2"/>
+      <sheetName val="05-065_she2"/>
+      <sheetName val="idgr_-_formula2"/>
+      <sheetName val="IDGR_(3)2"/>
+      <sheetName val="IDGR_(2)2"/>
+      <sheetName val="PLIV_(3)2"/>
+      <sheetName val="PLIV_(2)2"/>
+      <sheetName val="PLIV_(template)2"/>
+      <sheetName val="inv_recon2"/>
+      <sheetName val="side_member2"/>
+      <sheetName val="TTC_(FG)2"/>
+      <sheetName val="Sheet1_(3)2"/>
+      <sheetName val="truck_allocation2"/>
+      <sheetName val="Supplier_Price_Check2"/>
+      <sheetName val="$_-_june2"/>
+      <sheetName val="Vios_Cost_Reduction_actual_pro2"/>
+      <sheetName val="RET_PALLET2"/>
+      <sheetName val="Form_A2"/>
+      <sheetName val="NG_SUMMARY2"/>
+      <sheetName val="impact_pallet_and_racks2"/>
+      <sheetName val="Daily_WSD2"/>
+      <sheetName val="ass'y_12'04-05'053"/>
+      <sheetName val="Type_I2"/>
+      <sheetName val="Schedule_PM2"/>
+      <sheetName val="training_forklift2"/>
+      <sheetName val="Budget_by_Category2"/>
+      <sheetName val="investment_tmc_v8_0_34p2"/>
+      <sheetName val="PTD_Activity2"/>
+      <sheetName val="Sample_1PP_2"/>
+      <sheetName val="Open_Ran3"/>
+      <sheetName val="Open_RAN_23"/>
+      <sheetName val="CHIA_KH2"/>
+      <sheetName val="Purch__BP2"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0013"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0053"/>
+      <sheetName val="ＰＲＥ_NO1"/>
+      <sheetName val="Courier_4x2"/>
+      <sheetName val="Price_Trend2"/>
+      <sheetName val="車両仕様_?_x005f_x0012_?瞳?2"/>
+      <sheetName val="YARIS_HB2"/>
+      <sheetName val="00_KS"/>
+      <sheetName val="PRADO_3Dr_fl2"/>
+      <sheetName val="01_DATA2"/>
+      <sheetName val="Quality_Update2"/>
+      <sheetName val="prior_data"/>
+      <sheetName val="Table_Master"/>
+      <sheetName val="1_概述"/>
+      <sheetName val="Drop-down_Menu_List"/>
+      <sheetName val="Open_Item_List"/>
+      <sheetName val="本修正_DIFF_"/>
+      <sheetName val="Sector_Assignment"/>
+      <sheetName val="BQ_CONVEYOR"/>
+      <sheetName val="IMV_LIST_2003"/>
+      <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0000___x0"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000____瞳_"/>
+      <sheetName val="Part_list"/>
+      <sheetName val="INACT797"/>
+      <sheetName val="M1A"/>
+      <sheetName val="OK"/>
+      <sheetName val="??? Pilling upu_S y"/>
+      <sheetName val="ASF INVENTORY"/>
+      <sheetName val="車両仕様_4___x005f_x0013__x0013__x0013__x0013__x0013_"/>
+      <sheetName val="ጀጀ؀ԀЀࠀ᐀Ѐऀ܀̀܀ഀ܀Ԁऀ଀ࠀ_x0000_"/>
+      <sheetName val="CTable"/>
+      <sheetName val="bs is"/>
+      <sheetName val="成績"/>
+      <sheetName val="IT Checklist"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="No.31"/>
+      <sheetName val="コマンド認識, DTMF"/>
+      <sheetName val="CS2_SmcDriverインテグ項目"/>
+      <sheetName val="標準仕様DB"/>
+      <sheetName val="BEEP設定"/>
+      <sheetName val="休日"/>
+      <sheetName val="工数ｺｰﾄﾞﾘｽﾄ"/>
+      <sheetName val="5．キー入力動作説明"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="試験項目_R3小"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -13731,23 +14093,41 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35">
+      <sheetData sheetId="30">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="31">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="32">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="33">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="34" refreshError="1"/>
+      <sheetData sheetId="35" refreshError="1"/>
       <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
+      <sheetData sheetId="37" refreshError="1"/>
+      <sheetData sheetId="38" refreshError="1"/>
+      <sheetData sheetId="39" refreshError="1"/>
+      <sheetData sheetId="40" refreshError="1"/>
       <sheetData sheetId="41">
         <row r="1">
           <cell r="B1" t="str">
@@ -13769,8 +14149,20 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="44" refreshError="1"/>
-      <sheetData sheetId="45" refreshError="1"/>
+      <sheetData sheetId="44">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="45">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="46">
         <row r="1">
           <cell r="B1" t="str">
@@ -13779,29 +14171,65 @@
         </row>
       </sheetData>
       <sheetData sheetId="47" refreshError="1"/>
-      <sheetData sheetId="48"/>
+      <sheetData sheetId="48" refreshError="1"/>
       <sheetData sheetId="49" refreshError="1"/>
       <sheetData sheetId="50" refreshError="1"/>
-      <sheetData sheetId="51"/>
+      <sheetData sheetId="51" refreshError="1"/>
       <sheetData sheetId="52" refreshError="1"/>
-      <sheetData sheetId="53"/>
+      <sheetData sheetId="53" refreshError="1"/>
       <sheetData sheetId="54" refreshError="1"/>
       <sheetData sheetId="55" refreshError="1"/>
       <sheetData sheetId="56" refreshError="1"/>
       <sheetData sheetId="57" refreshError="1"/>
       <sheetData sheetId="58" refreshError="1"/>
-      <sheetData sheetId="59"/>
-      <sheetData sheetId="60"/>
-      <sheetData sheetId="61" refreshError="1"/>
-      <sheetData sheetId="62" refreshError="1"/>
-      <sheetData sheetId="63" refreshError="1"/>
-      <sheetData sheetId="64" refreshError="1"/>
+      <sheetData sheetId="59" refreshError="1"/>
+      <sheetData sheetId="60" refreshError="1"/>
+      <sheetData sheetId="61">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="62">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="63">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="64">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="65" refreshError="1"/>
       <sheetData sheetId="66" refreshError="1"/>
-      <sheetData sheetId="67"/>
-      <sheetData sheetId="68"/>
-      <sheetData sheetId="69" refreshError="1"/>
-      <sheetData sheetId="70" refreshError="1"/>
+      <sheetData sheetId="67" refreshError="1"/>
+      <sheetData sheetId="68" refreshError="1"/>
+      <sheetData sheetId="69">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="70">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="71" refreshError="1"/>
       <sheetData sheetId="72" refreshError="1"/>
       <sheetData sheetId="73" refreshError="1"/>
@@ -13891,7 +14319,7 @@
       <sheetData sheetId="157" refreshError="1"/>
       <sheetData sheetId="158" refreshError="1"/>
       <sheetData sheetId="159" refreshError="1"/>
-      <sheetData sheetId="160"/>
+      <sheetData sheetId="160" refreshError="1"/>
       <sheetData sheetId="161" refreshError="1"/>
       <sheetData sheetId="162" refreshError="1"/>
       <sheetData sheetId="163" refreshError="1"/>
@@ -13901,7 +14329,7 @@
       <sheetData sheetId="167" refreshError="1"/>
       <sheetData sheetId="168" refreshError="1"/>
       <sheetData sheetId="169" refreshError="1"/>
-      <sheetData sheetId="170" refreshError="1"/>
+      <sheetData sheetId="170"/>
       <sheetData sheetId="171" refreshError="1"/>
       <sheetData sheetId="172" refreshError="1"/>
       <sheetData sheetId="173" refreshError="1"/>
@@ -14038,33 +14466,45 @@
       <sheetData sheetId="304" refreshError="1"/>
       <sheetData sheetId="305" refreshError="1"/>
       <sheetData sheetId="306" refreshError="1"/>
-      <sheetData sheetId="307">
+      <sheetData sheetId="307" refreshError="1"/>
+      <sheetData sheetId="308" refreshError="1"/>
+      <sheetData sheetId="309" refreshError="1"/>
+      <sheetData sheetId="310" refreshError="1"/>
+      <sheetData sheetId="311">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="308">
+      <sheetData sheetId="312">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="309">
+      <sheetData sheetId="313">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="310"/>
-      <sheetData sheetId="311"/>
-      <sheetData sheetId="312" refreshError="1"/>
-      <sheetData sheetId="313" refreshError="1"/>
-      <sheetData sheetId="314" refreshError="1"/>
-      <sheetData sheetId="315" refreshError="1"/>
+      <sheetData sheetId="314">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="315">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="316" refreshError="1"/>
       <sheetData sheetId="317" refreshError="1"/>
       <sheetData sheetId="318" refreshError="1"/>
@@ -15636,8 +16076,8 @@
       </sheetData>
       <sheetData sheetId="793">
         <row r="1">
-          <cell r="B1" t="str">
-            <v>1</v>
+          <cell r="A1" t="str">
+            <v>ﾄﾖﾀ自動車株式会社　調達本部　</v>
           </cell>
         </row>
       </sheetData>
@@ -15673,7 +16113,13 @@
       <sheetData sheetId="805" refreshError="1"/>
       <sheetData sheetId="806" refreshError="1"/>
       <sheetData sheetId="807" refreshError="1"/>
-      <sheetData sheetId="808"/>
+      <sheetData sheetId="808">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="809" refreshError="1"/>
       <sheetData sheetId="810" refreshError="1"/>
       <sheetData sheetId="811" refreshError="1"/>
@@ -16636,9 +17082,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1050">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -16860,9 +17306,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1082">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -16881,9 +17327,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1085">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17210,9 +17656,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1132">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17301,9 +17747,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1145">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17532,16 +17978,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1178">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1179">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17581,9 +18027,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1185">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17609,9 +18055,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1189">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17630,9 +18076,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1192">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17700,9 +18146,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1202">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17721,16 +18167,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1205">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1206">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17742,16 +18188,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1208">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1209">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17791,9 +18237,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1215">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17819,9 +18265,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1219">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17840,9 +18286,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1222">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17910,9 +18356,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1232">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17931,16 +18377,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1235">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1236">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17952,16 +18398,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1238">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1239">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18001,16 +18447,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1245">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1246">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18070,16 +18516,76 @@
       <sheetData sheetId="1294"/>
       <sheetData sheetId="1295" refreshError="1"/>
       <sheetData sheetId="1296" refreshError="1"/>
-      <sheetData sheetId="1297"/>
-      <sheetData sheetId="1298"/>
-      <sheetData sheetId="1299"/>
-      <sheetData sheetId="1300"/>
-      <sheetData sheetId="1301"/>
-      <sheetData sheetId="1302"/>
-      <sheetData sheetId="1303"/>
-      <sheetData sheetId="1304"/>
-      <sheetData sheetId="1305"/>
-      <sheetData sheetId="1306"/>
+      <sheetData sheetId="1297">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1298">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1299">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1300">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1301">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1302">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1303">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1304">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1305">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1306">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1307" refreshError="1"/>
       <sheetData sheetId="1308" refreshError="1"/>
       <sheetData sheetId="1309" refreshError="1"/>
@@ -18089,13 +18595,13 @@
       <sheetData sheetId="1313" refreshError="1"/>
       <sheetData sheetId="1314" refreshError="1"/>
       <sheetData sheetId="1315" refreshError="1"/>
-      <sheetData sheetId="1316"/>
+      <sheetData sheetId="1316" refreshError="1"/>
       <sheetData sheetId="1317" refreshError="1"/>
       <sheetData sheetId="1318" refreshError="1"/>
       <sheetData sheetId="1319" refreshError="1"/>
       <sheetData sheetId="1320" refreshError="1"/>
       <sheetData sheetId="1321" refreshError="1"/>
-      <sheetData sheetId="1322" refreshError="1"/>
+      <sheetData sheetId="1322"/>
       <sheetData sheetId="1323" refreshError="1"/>
       <sheetData sheetId="1324" refreshError="1"/>
       <sheetData sheetId="1325" refreshError="1"/>
@@ -18190,39 +18696,33 @@
       <sheetData sheetId="1414" refreshError="1"/>
       <sheetData sheetId="1415" refreshError="1"/>
       <sheetData sheetId="1416" refreshError="1"/>
-      <sheetData sheetId="1417"/>
+      <sheetData sheetId="1417" refreshError="1"/>
       <sheetData sheetId="1418" refreshError="1"/>
       <sheetData sheetId="1419" refreshError="1"/>
       <sheetData sheetId="1420" refreshError="1"/>
       <sheetData sheetId="1421" refreshError="1"/>
       <sheetData sheetId="1422" refreshError="1"/>
-      <sheetData sheetId="1423"/>
-      <sheetData sheetId="1424"/>
-      <sheetData sheetId="1425"/>
-      <sheetData sheetId="1426"/>
+      <sheetData sheetId="1423" refreshError="1"/>
+      <sheetData sheetId="1424" refreshError="1"/>
+      <sheetData sheetId="1425" refreshError="1"/>
+      <sheetData sheetId="1426" refreshError="1"/>
       <sheetData sheetId="1427"/>
-      <sheetData sheetId="1428"/>
+      <sheetData sheetId="1428" refreshError="1"/>
       <sheetData sheetId="1429"/>
       <sheetData sheetId="1430"/>
       <sheetData sheetId="1431"/>
       <sheetData sheetId="1432"/>
       <sheetData sheetId="1433"/>
-      <sheetData sheetId="1434" refreshError="1"/>
-      <sheetData sheetId="1435">
-        <row r="3">
-          <cell r="C3" t="str">
-            <v>2022年</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1434"/>
+      <sheetData sheetId="1435"/>
       <sheetData sheetId="1436"/>
       <sheetData sheetId="1437"/>
       <sheetData sheetId="1438"/>
       <sheetData sheetId="1439"/>
-      <sheetData sheetId="1440"/>
-      <sheetData sheetId="1441"/>
-      <sheetData sheetId="1442"/>
-      <sheetData sheetId="1443"/>
+      <sheetData sheetId="1440" refreshError="1"/>
+      <sheetData sheetId="1441" refreshError="1"/>
+      <sheetData sheetId="1442" refreshError="1"/>
+      <sheetData sheetId="1443" refreshError="1"/>
       <sheetData sheetId="1444"/>
       <sheetData sheetId="1445"/>
       <sheetData sheetId="1446"/>
@@ -18234,8 +18734,14 @@
       <sheetData sheetId="1452"/>
       <sheetData sheetId="1453"/>
       <sheetData sheetId="1454"/>
-      <sheetData sheetId="1455"/>
-      <sheetData sheetId="1456"/>
+      <sheetData sheetId="1455" refreshError="1"/>
+      <sheetData sheetId="1456">
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>2022年</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1457"/>
       <sheetData sheetId="1458"/>
       <sheetData sheetId="1459"/>
@@ -18315,19 +18821,73 @@
       <sheetData sheetId="1533"/>
       <sheetData sheetId="1534"/>
       <sheetData sheetId="1535"/>
-      <sheetData sheetId="1536"/>
-      <sheetData sheetId="1537"/>
+      <sheetData sheetId="1536">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1537">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1538"/>
-      <sheetData sheetId="1539"/>
+      <sheetData sheetId="1539">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1540"/>
-      <sheetData sheetId="1541"/>
-      <sheetData sheetId="1542"/>
-      <sheetData sheetId="1543"/>
+      <sheetData sheetId="1541">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1542">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1543">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1544"/>
-      <sheetData sheetId="1545"/>
+      <sheetData sheetId="1545">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1546"/>
-      <sheetData sheetId="1547"/>
-      <sheetData sheetId="1548"/>
+      <sheetData sheetId="1547">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1548">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1549"/>
       <sheetData sheetId="1550"/>
       <sheetData sheetId="1551"/>
@@ -19717,52 +20277,52 @@
       <sheetData sheetId="2935"/>
       <sheetData sheetId="2936"/>
       <sheetData sheetId="2937"/>
-      <sheetData sheetId="2938">
-        <row r="1">
-          <cell r="A1"/>
-        </row>
-      </sheetData>
+      <sheetData sheetId="2938"/>
       <sheetData sheetId="2939"/>
       <sheetData sheetId="2940"/>
       <sheetData sheetId="2941"/>
-      <sheetData sheetId="2942" refreshError="1"/>
-      <sheetData sheetId="2943">
+      <sheetData sheetId="2942"/>
+      <sheetData sheetId="2943"/>
+      <sheetData sheetId="2944"/>
+      <sheetData sheetId="2945"/>
+      <sheetData sheetId="2946"/>
+      <sheetData sheetId="2947"/>
+      <sheetData sheetId="2948"/>
+      <sheetData sheetId="2949"/>
+      <sheetData sheetId="2950"/>
+      <sheetData sheetId="2951"/>
+      <sheetData sheetId="2952"/>
+      <sheetData sheetId="2953"/>
+      <sheetData sheetId="2954"/>
+      <sheetData sheetId="2955"/>
+      <sheetData sheetId="2956"/>
+      <sheetData sheetId="2957"/>
+      <sheetData sheetId="2958"/>
+      <sheetData sheetId="2959">
+        <row r="1">
+          <cell r="A1"/>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2960"/>
+      <sheetData sheetId="2961"/>
+      <sheetData sheetId="2962"/>
+      <sheetData sheetId="2963">
         <row r="1">
           <cell r="B1" t="str">
             <v>文章管理番号</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2944"/>
-      <sheetData sheetId="2945" refreshError="1"/>
-      <sheetData sheetId="2946" refreshError="1"/>
-      <sheetData sheetId="2947" refreshError="1"/>
-      <sheetData sheetId="2948" refreshError="1"/>
-      <sheetData sheetId="2949" refreshError="1"/>
-      <sheetData sheetId="2950" refreshError="1"/>
-      <sheetData sheetId="2951" refreshError="1"/>
-      <sheetData sheetId="2952" refreshError="1"/>
-      <sheetData sheetId="2953" refreshError="1"/>
-      <sheetData sheetId="2954" refreshError="1"/>
-      <sheetData sheetId="2955" refreshError="1"/>
-      <sheetData sheetId="2956" refreshError="1"/>
-      <sheetData sheetId="2957" refreshError="1"/>
-      <sheetData sheetId="2958" refreshError="1"/>
-      <sheetData sheetId="2959" refreshError="1"/>
-      <sheetData sheetId="2960" refreshError="1"/>
-      <sheetData sheetId="2961" refreshError="1"/>
-      <sheetData sheetId="2962" refreshError="1"/>
-      <sheetData sheetId="2963"/>
       <sheetData sheetId="2964"/>
-      <sheetData sheetId="2965"/>
-      <sheetData sheetId="2966"/>
-      <sheetData sheetId="2967"/>
-      <sheetData sheetId="2968"/>
-      <sheetData sheetId="2969"/>
-      <sheetData sheetId="2970"/>
-      <sheetData sheetId="2971"/>
-      <sheetData sheetId="2972"/>
-      <sheetData sheetId="2973"/>
+      <sheetData sheetId="2965" refreshError="1"/>
+      <sheetData sheetId="2966" refreshError="1"/>
+      <sheetData sheetId="2967" refreshError="1"/>
+      <sheetData sheetId="2968" refreshError="1"/>
+      <sheetData sheetId="2969" refreshError="1"/>
+      <sheetData sheetId="2970" refreshError="1"/>
+      <sheetData sheetId="2971" refreshError="1"/>
+      <sheetData sheetId="2972" refreshError="1"/>
+      <sheetData sheetId="2973" refreshError="1"/>
       <sheetData sheetId="2974" refreshError="1"/>
       <sheetData sheetId="2975"/>
       <sheetData sheetId="2976" refreshError="1"/>
@@ -19774,6 +20334,323 @@
       <sheetData sheetId="2982" refreshError="1"/>
       <sheetData sheetId="2983" refreshError="1"/>
       <sheetData sheetId="2984" refreshError="1"/>
+      <sheetData sheetId="2985" refreshError="1"/>
+      <sheetData sheetId="2986" refreshError="1"/>
+      <sheetData sheetId="2987" refreshError="1"/>
+      <sheetData sheetId="2988" refreshError="1"/>
+      <sheetData sheetId="2989" refreshError="1"/>
+      <sheetData sheetId="2990" refreshError="1"/>
+      <sheetData sheetId="2991" refreshError="1"/>
+      <sheetData sheetId="2992" refreshError="1"/>
+      <sheetData sheetId="2993" refreshError="1"/>
+      <sheetData sheetId="2994" refreshError="1"/>
+      <sheetData sheetId="2995" refreshError="1"/>
+      <sheetData sheetId="2996" refreshError="1"/>
+      <sheetData sheetId="2997" refreshError="1"/>
+      <sheetData sheetId="2998" refreshError="1"/>
+      <sheetData sheetId="2999" refreshError="1"/>
+      <sheetData sheetId="3000" refreshError="1"/>
+      <sheetData sheetId="3001" refreshError="1"/>
+      <sheetData sheetId="3002" refreshError="1"/>
+      <sheetData sheetId="3003" refreshError="1"/>
+      <sheetData sheetId="3004" refreshError="1"/>
+      <sheetData sheetId="3005" refreshError="1"/>
+      <sheetData sheetId="3006" refreshError="1"/>
+      <sheetData sheetId="3007" refreshError="1"/>
+      <sheetData sheetId="3008" refreshError="1"/>
+      <sheetData sheetId="3009" refreshError="1"/>
+      <sheetData sheetId="3010" refreshError="1"/>
+      <sheetData sheetId="3011" refreshError="1"/>
+      <sheetData sheetId="3012" refreshError="1"/>
+      <sheetData sheetId="3013" refreshError="1"/>
+      <sheetData sheetId="3014" refreshError="1"/>
+      <sheetData sheetId="3015" refreshError="1"/>
+      <sheetData sheetId="3016" refreshError="1"/>
+      <sheetData sheetId="3017" refreshError="1"/>
+      <sheetData sheetId="3018" refreshError="1"/>
+      <sheetData sheetId="3019" refreshError="1"/>
+      <sheetData sheetId="3020" refreshError="1"/>
+      <sheetData sheetId="3021" refreshError="1"/>
+      <sheetData sheetId="3022" refreshError="1"/>
+      <sheetData sheetId="3023" refreshError="1"/>
+      <sheetData sheetId="3024" refreshError="1"/>
+      <sheetData sheetId="3025" refreshError="1"/>
+      <sheetData sheetId="3026" refreshError="1"/>
+      <sheetData sheetId="3027" refreshError="1"/>
+      <sheetData sheetId="3028" refreshError="1"/>
+      <sheetData sheetId="3029" refreshError="1"/>
+      <sheetData sheetId="3030" refreshError="1"/>
+      <sheetData sheetId="3031" refreshError="1"/>
+      <sheetData sheetId="3032" refreshError="1"/>
+      <sheetData sheetId="3033" refreshError="1"/>
+      <sheetData sheetId="3034"/>
+      <sheetData sheetId="3035"/>
+      <sheetData sheetId="3036"/>
+      <sheetData sheetId="3037"/>
+      <sheetData sheetId="3038"/>
+      <sheetData sheetId="3039"/>
+      <sheetData sheetId="3040"/>
+      <sheetData sheetId="3041"/>
+      <sheetData sheetId="3042"/>
+      <sheetData sheetId="3043"/>
+      <sheetData sheetId="3044"/>
+      <sheetData sheetId="3045"/>
+      <sheetData sheetId="3046"/>
+      <sheetData sheetId="3047"/>
+      <sheetData sheetId="3048"/>
+      <sheetData sheetId="3049"/>
+      <sheetData sheetId="3050"/>
+      <sheetData sheetId="3051"/>
+      <sheetData sheetId="3052"/>
+      <sheetData sheetId="3053"/>
+      <sheetData sheetId="3054"/>
+      <sheetData sheetId="3055"/>
+      <sheetData sheetId="3056"/>
+      <sheetData sheetId="3057"/>
+      <sheetData sheetId="3058"/>
+      <sheetData sheetId="3059"/>
+      <sheetData sheetId="3060"/>
+      <sheetData sheetId="3061"/>
+      <sheetData sheetId="3062"/>
+      <sheetData sheetId="3063"/>
+      <sheetData sheetId="3064"/>
+      <sheetData sheetId="3065"/>
+      <sheetData sheetId="3066"/>
+      <sheetData sheetId="3067"/>
+      <sheetData sheetId="3068"/>
+      <sheetData sheetId="3069"/>
+      <sheetData sheetId="3070"/>
+      <sheetData sheetId="3071"/>
+      <sheetData sheetId="3072"/>
+      <sheetData sheetId="3073"/>
+      <sheetData sheetId="3074"/>
+      <sheetData sheetId="3075"/>
+      <sheetData sheetId="3076"/>
+      <sheetData sheetId="3077">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3078">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3079">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3080">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3081">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3082">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3083">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3084">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3085">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3086">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3087">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3088">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3089">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3090">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3091">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3092">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3093">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3094">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3095">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3096">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3097">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3098">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3099">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3100"/>
+      <sheetData sheetId="3101"/>
+      <sheetData sheetId="3102"/>
+      <sheetData sheetId="3103"/>
+      <sheetData sheetId="3104"/>
+      <sheetData sheetId="3105"/>
+      <sheetData sheetId="3106"/>
+      <sheetData sheetId="3107"/>
+      <sheetData sheetId="3108"/>
+      <sheetData sheetId="3109"/>
+      <sheetData sheetId="3110"/>
+      <sheetData sheetId="3111"/>
+      <sheetData sheetId="3112"/>
+      <sheetData sheetId="3113"/>
+      <sheetData sheetId="3114"/>
+      <sheetData sheetId="3115"/>
+      <sheetData sheetId="3116"/>
+      <sheetData sheetId="3117"/>
+      <sheetData sheetId="3118"/>
+      <sheetData sheetId="3119"/>
+      <sheetData sheetId="3120"/>
+      <sheetData sheetId="3121"/>
+      <sheetData sheetId="3122"/>
+      <sheetData sheetId="3123"/>
+      <sheetData sheetId="3124"/>
+      <sheetData sheetId="3125"/>
+      <sheetData sheetId="3126"/>
+      <sheetData sheetId="3127"/>
+      <sheetData sheetId="3128"/>
+      <sheetData sheetId="3129"/>
+      <sheetData sheetId="3130"/>
+      <sheetData sheetId="3131"/>
+      <sheetData sheetId="3132"/>
+      <sheetData sheetId="3133"/>
+      <sheetData sheetId="3134"/>
+      <sheetData sheetId="3135"/>
+      <sheetData sheetId="3136"/>
+      <sheetData sheetId="3137" refreshError="1"/>
+      <sheetData sheetId="3138" refreshError="1"/>
+      <sheetData sheetId="3139" refreshError="1"/>
+      <sheetData sheetId="3140" refreshError="1"/>
+      <sheetData sheetId="3141" refreshError="1"/>
+      <sheetData sheetId="3142" refreshError="1"/>
+      <sheetData sheetId="3143" refreshError="1"/>
+      <sheetData sheetId="3144" refreshError="1"/>
+      <sheetData sheetId="3145" refreshError="1"/>
+      <sheetData sheetId="3146" refreshError="1"/>
+      <sheetData sheetId="3147" refreshError="1"/>
+      <sheetData sheetId="3148" refreshError="1"/>
+      <sheetData sheetId="3149" refreshError="1"/>
+      <sheetData sheetId="3150" refreshError="1"/>
+      <sheetData sheetId="3151" refreshError="1"/>
+      <sheetData sheetId="3152" refreshError="1"/>
+      <sheetData sheetId="3153" refreshError="1"/>
+      <sheetData sheetId="3154" refreshError="1"/>
+      <sheetData sheetId="3155" refreshError="1"/>
+      <sheetData sheetId="3156" refreshError="1"/>
+      <sheetData sheetId="3157" refreshError="1"/>
+      <sheetData sheetId="3158" refreshError="1"/>
+      <sheetData sheetId="3159" refreshError="1"/>
+      <sheetData sheetId="3160" refreshError="1"/>
+      <sheetData sheetId="3161" refreshError="1"/>
+      <sheetData sheetId="3162" refreshError="1"/>
+      <sheetData sheetId="3163" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -19868,17 +20745,62 @@
       <sheetName val="_UnderConst_Analysis"/>
       <sheetName val="アップロード系(2)"/>
       <sheetName val="List"/>
+      <sheetName val="パラメータ設定表"/>
       <sheetName val="別紙7_操作系イベント発生時_"/>
       <sheetName val="別紙11_各競合条件における起動可否_"/>
       <sheetName val="index"/>
-      <sheetName val="パラメータ設定表"/>
+      <sheetName val="入力"/>
+      <sheetName val="415T戟L"/>
+      <sheetName val="No.31"/>
       <sheetName val="改訂履歴"/>
       <sheetName val="リスト"/>
       <sheetName val="ドメイン"/>
       <sheetName val="format"/>
-      <sheetName val="入力"/>
-      <sheetName val="415T戟L"/>
-      <sheetName val="No.31"/>
+      <sheetName val="Navigation"/>
+      <sheetName val="Cover"/>
+      <sheetName val="DataList"/>
+      <sheetName val="変更要件"/>
+      <sheetName val="【石倉編集中】DisplayStateTransitionTa"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="Data"/>
+      <sheetName val="★VarUsed"/>
+      <sheetName val="輝度計算(直線用)"/>
+      <sheetName val="コード_dimautocon"/>
+      <sheetName val="パラメータ_dimautocon"/>
+      <sheetName val="パラメータ_dimcalprcnt"/>
+      <sheetName val="パラメータ_dimmanualstep"/>
+      <sheetName val="パラメータ_dimmgr"/>
+      <sheetName val="XX-0080"/>
+      <sheetName val="メッセージ定義"/>
+      <sheetName val="XX-0180"/>
+      <sheetName val="lock"/>
+      <sheetName val="level"/>
+      <sheetName val="cominf"/>
+      <sheetName val="disconnect"/>
+      <sheetName val="９ｘ"/>
+      <sheetName val="Ｂｘ"/>
+      <sheetName val="Ｃｘ"/>
+      <sheetName val="Ｅｘ"/>
+      <sheetName val="休日"/>
+      <sheetName val="HMI-004_Screen（old）"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="MOTO"/>
+      <sheetName val="前提書情報"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="module"/>
+      <sheetName val="選択肢"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="メニュー"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="R0-10表紙MIC"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="修正ﾌｧｲﾙ一覧"/>
+      <sheetName val="RGB"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -19977,6 +20899,51 @@
       <sheetData sheetId="93" refreshError="1"/>
       <sheetData sheetId="94" refreshError="1"/>
       <sheetData sheetId="95" refreshError="1"/>
+      <sheetData sheetId="96" refreshError="1"/>
+      <sheetData sheetId="97" refreshError="1"/>
+      <sheetData sheetId="98" refreshError="1"/>
+      <sheetData sheetId="99" refreshError="1"/>
+      <sheetData sheetId="100" refreshError="1"/>
+      <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
+      <sheetData sheetId="133" refreshError="1"/>
+      <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -20293,10 +21260,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="52" width="2.125" style="235" customWidth="1"/>
-    <col min="53" max="16384" width="8.125" style="235"/>
+    <col min="1" max="52" width="2.08984375" style="235" customWidth="1"/>
+    <col min="53" max="16384" width="8.08984375" style="235"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -20354,32 +21321,32 @@
       <c r="AJ33" s="239"/>
     </row>
     <row r="34" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y34" s="238" t="s">
-        <v>288</v>
+      <c r="Y34" s="157" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="253" t="s">
-        <v>289</v>
-      </c>
-      <c r="Z35" s="254"/>
-      <c r="AA35" s="254"/>
-      <c r="AB35" s="254"/>
-      <c r="AC35" s="255"/>
-      <c r="AD35" s="253" t="s">
-        <v>290</v>
-      </c>
-      <c r="AE35" s="254"/>
-      <c r="AF35" s="254"/>
-      <c r="AG35" s="254"/>
-      <c r="AH35" s="255"/>
-      <c r="AI35" s="253" t="s">
-        <v>291</v>
-      </c>
-      <c r="AJ35" s="254"/>
-      <c r="AK35" s="254"/>
-      <c r="AL35" s="254"/>
-      <c r="AM35" s="255"/>
+      <c r="Y35" s="258" t="s">
+        <v>286</v>
+      </c>
+      <c r="Z35" s="259"/>
+      <c r="AA35" s="259"/>
+      <c r="AB35" s="259"/>
+      <c r="AC35" s="260"/>
+      <c r="AD35" s="258" t="s">
+        <v>287</v>
+      </c>
+      <c r="AE35" s="259"/>
+      <c r="AF35" s="259"/>
+      <c r="AG35" s="259"/>
+      <c r="AH35" s="260"/>
+      <c r="AI35" s="258" t="s">
+        <v>288</v>
+      </c>
+      <c r="AJ35" s="259"/>
+      <c r="AK35" s="259"/>
+      <c r="AL35" s="259"/>
+      <c r="AM35" s="260"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
       <c r="D36" s="239"/>
@@ -20425,21 +21392,21 @@
       <c r="Y38" s="244"/>
       <c r="Z38" s="239"/>
       <c r="AA38" s="240" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AB38" s="239"/>
       <c r="AC38" s="246"/>
       <c r="AD38" s="244"/>
       <c r="AE38" s="239"/>
       <c r="AF38" s="240" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AG38" s="239"/>
       <c r="AH38" s="246"/>
       <c r="AI38" s="247"/>
       <c r="AJ38" s="239"/>
       <c r="AK38" s="240" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AL38" s="239"/>
       <c r="AM38" s="246"/>
@@ -20474,31 +21441,31 @@
     <row r="41" spans="3:39" ht="13.15" customHeight="1"/>
     <row r="42" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y42" s="238" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="253" t="s">
-        <v>289</v>
-      </c>
-      <c r="Z43" s="254"/>
-      <c r="AA43" s="254"/>
-      <c r="AB43" s="254"/>
-      <c r="AC43" s="255"/>
-      <c r="AD43" s="253" t="s">
-        <v>290</v>
-      </c>
-      <c r="AE43" s="254"/>
-      <c r="AF43" s="254"/>
-      <c r="AG43" s="254"/>
-      <c r="AH43" s="255"/>
-      <c r="AI43" s="253" t="s">
-        <v>291</v>
-      </c>
-      <c r="AJ43" s="254"/>
-      <c r="AK43" s="254"/>
-      <c r="AL43" s="254"/>
-      <c r="AM43" s="255"/>
+      <c r="Y43" s="258" t="s">
+        <v>286</v>
+      </c>
+      <c r="Z43" s="259"/>
+      <c r="AA43" s="259"/>
+      <c r="AB43" s="259"/>
+      <c r="AC43" s="260"/>
+      <c r="AD43" s="258" t="s">
+        <v>287</v>
+      </c>
+      <c r="AE43" s="259"/>
+      <c r="AF43" s="259"/>
+      <c r="AG43" s="259"/>
+      <c r="AH43" s="260"/>
+      <c r="AI43" s="258" t="s">
+        <v>288</v>
+      </c>
+      <c r="AJ43" s="259"/>
+      <c r="AK43" s="259"/>
+      <c r="AL43" s="259"/>
+      <c r="AM43" s="260"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
       <c r="D44" s="239"/>
@@ -20544,21 +21511,21 @@
       <c r="Y46" s="244"/>
       <c r="Z46" s="239"/>
       <c r="AA46" s="240" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AB46" s="239"/>
       <c r="AC46" s="246"/>
       <c r="AD46" s="239"/>
       <c r="AE46" s="239"/>
       <c r="AF46" s="240" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG46" s="239"/>
       <c r="AH46" s="246"/>
       <c r="AI46" s="247"/>
       <c r="AJ46" s="239"/>
       <c r="AK46" s="240" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AL46" s="239"/>
       <c r="AM46" s="246"/>
@@ -20592,31 +21559,31 @@
     <row r="49" spans="4:39" ht="13.15" customHeight="1"/>
     <row r="50" spans="4:39" ht="13.15" customHeight="1">
       <c r="Y50" s="238" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="253" t="s">
-        <v>289</v>
-      </c>
-      <c r="Z51" s="254"/>
-      <c r="AA51" s="254"/>
-      <c r="AB51" s="254"/>
-      <c r="AC51" s="255"/>
-      <c r="AD51" s="253" t="s">
-        <v>290</v>
-      </c>
-      <c r="AE51" s="254"/>
-      <c r="AF51" s="254"/>
-      <c r="AG51" s="254"/>
-      <c r="AH51" s="255"/>
-      <c r="AI51" s="253" t="s">
-        <v>291</v>
-      </c>
-      <c r="AJ51" s="254"/>
-      <c r="AK51" s="254"/>
-      <c r="AL51" s="254"/>
-      <c r="AM51" s="255"/>
+      <c r="Y51" s="258" t="s">
+        <v>286</v>
+      </c>
+      <c r="Z51" s="259"/>
+      <c r="AA51" s="259"/>
+      <c r="AB51" s="259"/>
+      <c r="AC51" s="260"/>
+      <c r="AD51" s="258" t="s">
+        <v>287</v>
+      </c>
+      <c r="AE51" s="259"/>
+      <c r="AF51" s="259"/>
+      <c r="AG51" s="259"/>
+      <c r="AH51" s="260"/>
+      <c r="AI51" s="258" t="s">
+        <v>288</v>
+      </c>
+      <c r="AJ51" s="259"/>
+      <c r="AK51" s="259"/>
+      <c r="AL51" s="259"/>
+      <c r="AM51" s="260"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
       <c r="D52" s="239"/>
@@ -20662,21 +21629,21 @@
       <c r="Y54" s="244"/>
       <c r="Z54" s="239"/>
       <c r="AA54" s="240" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AB54" s="239"/>
       <c r="AC54" s="246"/>
       <c r="AD54" s="239"/>
       <c r="AE54" s="239"/>
       <c r="AF54" s="240" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AG54" s="239"/>
       <c r="AH54" s="246"/>
       <c r="AI54" s="247"/>
       <c r="AJ54" s="239"/>
       <c r="AK54" s="240" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AL54" s="239"/>
       <c r="AM54" s="246"/>
@@ -20707,7 +21674,7 @@
     </row>
     <row r="57" spans="4:39" ht="13.15" customHeight="1">
       <c r="AK57" s="235" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -20733,14 +21700,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="4.5" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.5" customWidth="1"/>
-    <col min="5" max="6" width="12.875" hidden="1" customWidth="1"/>
-    <col min="7" max="22" width="13.125" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="13.125" customWidth="1"/>
+    <col min="4" max="4" width="69.453125" customWidth="1"/>
+    <col min="5" max="6" width="12.90625" hidden="1" customWidth="1"/>
+    <col min="7" max="22" width="13.08984375" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -20751,18 +21718,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="256" t="s">
+      <c r="I2" s="261" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
-      <c r="M2" s="256"/>
-      <c r="N2" s="256"/>
-      <c r="O2" s="256"/>
-      <c r="P2" s="256"/>
-      <c r="Q2" s="256"/>
-      <c r="R2" s="256"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="261"/>
+      <c r="O2" s="261"/>
+      <c r="P2" s="261"/>
+      <c r="Q2" s="261"/>
+      <c r="R2" s="261"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -20775,25 +21742,25 @@
       <c r="H3" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="257" t="s">
+      <c r="I3" s="262" t="s">
         <v>203</v>
       </c>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
-      <c r="M3" s="258"/>
-      <c r="N3" s="258"/>
-      <c r="O3" s="258"/>
-      <c r="P3" s="258"/>
-      <c r="Q3" s="258"/>
-      <c r="R3" s="258"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
+      <c r="M3" s="263"/>
+      <c r="N3" s="263"/>
+      <c r="O3" s="263"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="22" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.0.1</v>
+        <v>1.0.2</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -20807,45 +21774,45 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B14)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
+    <row r="7" spans="2:24">
+      <c r="C7" s="266" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="267"/>
+      <c r="E7" s="268" t="s">
         <v>2</v>
       </c>
+      <c r="F7" s="268"/>
+      <c r="G7" s="269" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="269"/>
+      <c r="I7" s="269"/>
+      <c r="J7" s="269"/>
+      <c r="K7" s="269"/>
+      <c r="L7" s="269"/>
+      <c r="M7" s="270" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="270"/>
+      <c r="O7" s="270"/>
+      <c r="P7" s="270"/>
+      <c r="Q7" s="270"/>
+      <c r="R7" s="271"/>
+      <c r="S7" s="264" t="s">
+        <v>279</v>
+      </c>
+      <c r="T7" s="264"/>
+      <c r="U7" s="264"/>
+      <c r="V7" s="264"/>
+      <c r="W7" s="264"/>
+      <c r="X7" s="265"/>
     </row>
-    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
-    <row r="7" spans="2:24">
-      <c r="C7" s="261" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="262"/>
-      <c r="E7" s="263" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="263"/>
-      <c r="G7" s="264" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="264"/>
-      <c r="I7" s="264"/>
-      <c r="J7" s="264"/>
-      <c r="K7" s="264"/>
-      <c r="L7" s="264"/>
-      <c r="M7" s="265" t="s">
-        <v>12</v>
-      </c>
-      <c r="N7" s="265"/>
-      <c r="O7" s="265"/>
-      <c r="P7" s="265"/>
-      <c r="Q7" s="265"/>
-      <c r="R7" s="266"/>
-      <c r="S7" s="259" t="s">
-        <v>281</v>
-      </c>
-      <c r="T7" s="259"/>
-      <c r="U7" s="259"/>
-      <c r="V7" s="259"/>
-      <c r="W7" s="259"/>
-      <c r="X7" s="260"/>
-    </row>
-    <row r="8" spans="2:24" ht="27.75" thickBot="1">
+    <row r="8" spans="2:24" ht="26.5" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>93</v>
       </c>
@@ -20898,7 +21865,7 @@
         <v>11</v>
       </c>
       <c r="S8" s="16" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="T8" s="16" t="s">
         <v>7</v>
@@ -20916,22 +21883,22 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="14.25" thickTop="1">
+    <row r="9" spans="2:24" ht="13.5" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>31</v>
@@ -20952,13 +21919,13 @@
         <v>31</v>
       </c>
       <c r="M9" s="251" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="N9" s="252">
         <v>43943</v>
       </c>
       <c r="O9" s="251" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P9" s="252">
         <v>43943</v>
@@ -20988,16 +21955,16 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="40.5">
+    <row r="10" spans="2:24" ht="39">
       <c r="B10" s="9">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D10" s="234" t="s">
         <v>285</v>
-      </c>
-      <c r="D10" s="234" t="s">
-        <v>287</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>31</v>
@@ -21034,21 +22001,29 @@
       <c r="U10" s="1"/>
       <c r="V10" s="231"/>
       <c r="W10" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="X10" s="232">
         <v>45806</v>
       </c>
     </row>
-    <row r="11" spans="2:24">
+    <row r="11" spans="2:24" ht="91">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="C11" s="253" t="s">
+        <v>302</v>
+      </c>
+      <c r="D11" s="254" t="s">
+        <v>304</v>
+      </c>
+      <c r="E11" s="255" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="255" t="s">
+        <v>31</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -21065,8 +22040,12 @@
       <c r="T11" s="231"/>
       <c r="U11" s="1"/>
       <c r="V11" s="231"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="232"/>
+      <c r="W11" s="256" t="s">
+        <v>301</v>
+      </c>
+      <c r="X11" s="257">
+        <v>46008</v>
+      </c>
     </row>
     <row r="12" spans="2:24">
       <c r="B12" s="9">
@@ -21096,7 +22075,7 @@
       <c r="W12" s="1"/>
       <c r="X12" s="232"/>
     </row>
-    <row r="13" spans="2:24" ht="14.25" thickBot="1">
+    <row r="13" spans="2:24" ht="13.5" thickBot="1">
       <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -21150,11 +22129,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.625" customWidth="1"/>
-    <col min="3" max="3" width="3.5" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="4.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.453125" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21168,13 +22147,13 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.25" thickBot="1">
+    <row r="6" spans="2:5" ht="13.5" thickBot="1">
       <c r="B6" s="157" t="s">
         <v>135</v>
       </c>
       <c r="C6" s="157"/>
     </row>
-    <row r="7" spans="2:5" ht="14.25" thickBot="1">
+    <row r="7" spans="2:5" ht="13.5" thickBot="1">
       <c r="C7" s="82" t="s">
         <v>137</v>
       </c>
@@ -21194,7 +22173,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="27">
+    <row r="9" spans="2:5" ht="26">
       <c r="C9" s="167">
         <v>1</v>
       </c>
@@ -21205,7 +22184,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="14.25" thickBot="1">
+    <row r="10" spans="2:5" ht="13.5" thickBot="1">
       <c r="C10" s="165"/>
       <c r="D10" s="93"/>
       <c r="E10" s="5"/>
@@ -21213,14 +22192,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="163"/>
     </row>
-    <row r="12" spans="2:5" ht="14.25" thickBot="1">
+    <row r="12" spans="2:5" ht="13.5" thickBot="1">
       <c r="B12" s="158" t="s">
         <v>136</v>
       </c>
       <c r="C12" s="89"/>
       <c r="D12" s="89"/>
     </row>
-    <row r="13" spans="2:5" ht="14.25" thickBot="1">
+    <row r="13" spans="2:5" ht="13.5" thickBot="1">
       <c r="B13" s="159"/>
       <c r="C13" s="164" t="s">
         <v>137</v>
@@ -21232,7 +22211,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="14.25" thickTop="1">
+    <row r="14" spans="2:5" ht="13.5" thickTop="1">
       <c r="C14" s="161">
         <v>0</v>
       </c>
@@ -21309,17 +22288,17 @@
         <v>174</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="14.25" thickBot="1">
+    <row r="21" spans="2:5" ht="13.5" thickBot="1">
       <c r="C21" s="165"/>
       <c r="D21" s="93"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="14.25" thickBot="1">
+    <row r="24" spans="2:5" ht="13.5" thickBot="1">
       <c r="B24" s="157" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="14.25" thickBot="1">
+    <row r="25" spans="2:5" ht="13.5" thickBot="1">
       <c r="C25" s="164" t="s">
         <v>137</v>
       </c>
@@ -21406,26 +22385,26 @@
       <c r="D33" s="92"/>
       <c r="E33" s="78"/>
     </row>
-    <row r="34" spans="2:5" ht="14.25" thickBot="1">
+    <row r="34" spans="2:5" ht="13.5" thickBot="1">
       <c r="C34" s="165"/>
       <c r="D34" s="93"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="14.25" thickBot="1">
+    <row r="37" spans="2:5" ht="13.5" thickBot="1">
       <c r="B37" s="157" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="267"/>
-      <c r="D38" s="268"/>
+      <c r="C38" s="272"/>
+      <c r="D38" s="273"/>
       <c r="E38" s="118" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="14.25" thickBot="1">
-      <c r="C39" s="269"/>
-      <c r="D39" s="270"/>
+    <row r="39" spans="2:5" ht="13.5" thickBot="1">
+      <c r="C39" s="274"/>
+      <c r="D39" s="275"/>
       <c r="E39" s="5" t="s">
         <v>125</v>
       </c>
@@ -21454,133 +22433,133 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.875" customWidth="1"/>
-    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.90625" customWidth="1"/>
+    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="296" t="s">
+      <c r="B2" s="301" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="297"/>
-      <c r="D2" s="284" t="s">
-        <v>216</v>
-      </c>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="286"/>
+      <c r="C2" s="302"/>
+      <c r="D2" s="289" t="s">
+        <v>215</v>
+      </c>
+      <c r="E2" s="290"/>
+      <c r="F2" s="290"/>
+      <c r="G2" s="290"/>
+      <c r="H2" s="291"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="271" t="s">
+      <c r="B3" s="276" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="272"/>
-      <c r="D3" s="287" t="s">
+      <c r="C3" s="277"/>
+      <c r="D3" s="292" t="s">
         <v>209</v>
       </c>
-      <c r="E3" s="288"/>
-      <c r="F3" s="288"/>
-      <c r="G3" s="288"/>
-      <c r="H3" s="289"/>
+      <c r="E3" s="293"/>
+      <c r="F3" s="293"/>
+      <c r="G3" s="293"/>
+      <c r="H3" s="294"/>
     </row>
-    <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="282" t="s">
+    <row r="4" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B4" s="287" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="283"/>
-      <c r="D4" s="290" t="str">
+      <c r="C4" s="288"/>
+      <c r="D4" s="295" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_B_AVAS-CSTD-0-00-A-C0.c</v>
       </c>
-      <c r="E4" s="291"/>
-      <c r="F4" s="291"/>
-      <c r="G4" s="291"/>
-      <c r="H4" s="292"/>
+      <c r="E4" s="296"/>
+      <c r="F4" s="296"/>
+      <c r="G4" s="296"/>
+      <c r="H4" s="297"/>
     </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1">
+    <row r="5" spans="2:14" ht="13.5" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="296" t="s">
+      <c r="B6" s="301" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="297"/>
-      <c r="D6" s="293" t="str">
+      <c r="C6" s="302"/>
+      <c r="D6" s="298" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>B_AVAS</v>
       </c>
-      <c r="E6" s="294"/>
-      <c r="F6" s="294"/>
-      <c r="G6" s="294"/>
-      <c r="H6" s="295"/>
+      <c r="E6" s="299"/>
+      <c r="F6" s="299"/>
+      <c r="G6" s="299"/>
+      <c r="H6" s="300"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="271" t="s">
+      <c r="B7" s="276" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="272"/>
-      <c r="D7" s="273">
+      <c r="C7" s="277"/>
+      <c r="D7" s="278">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="274"/>
-      <c r="F7" s="274"/>
-      <c r="G7" s="274"/>
-      <c r="H7" s="275"/>
+      <c r="E7" s="279"/>
+      <c r="F7" s="279"/>
+      <c r="G7" s="279"/>
+      <c r="H7" s="280"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="271" t="s">
+      <c r="B8" s="276" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="272"/>
-      <c r="D8" s="273" t="str">
+      <c r="C8" s="277"/>
+      <c r="D8" s="278" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_B_AVAS_MTRX</v>
       </c>
-      <c r="E8" s="274"/>
-      <c r="F8" s="274"/>
-      <c r="G8" s="274"/>
-      <c r="H8" s="275"/>
+      <c r="E8" s="279"/>
+      <c r="F8" s="279"/>
+      <c r="G8" s="279"/>
+      <c r="H8" s="280"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="271" t="s">
+      <c r="B9" s="276" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="272"/>
-      <c r="D9" s="276" t="s">
+      <c r="C9" s="277"/>
+      <c r="D9" s="281" t="s">
         <v>207</v>
       </c>
-      <c r="E9" s="277"/>
-      <c r="F9" s="277"/>
-      <c r="G9" s="277"/>
-      <c r="H9" s="278"/>
+      <c r="E9" s="282"/>
+      <c r="F9" s="282"/>
+      <c r="G9" s="282"/>
+      <c r="H9" s="283"/>
     </row>
-    <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="282" t="s">
+    <row r="10" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B10" s="287" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="283"/>
-      <c r="D10" s="279">
+      <c r="C10" s="288"/>
+      <c r="D10" s="284">
         <v>103</v>
       </c>
-      <c r="E10" s="280"/>
-      <c r="F10" s="280"/>
-      <c r="G10" s="280"/>
-      <c r="H10" s="281"/>
+      <c r="E10" s="285"/>
+      <c r="F10" s="285"/>
+      <c r="G10" s="285"/>
+      <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
-    <row r="12" spans="2:14" ht="14.25" thickBot="1">
+    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.5" thickBot="1">
       <c r="B12" s="148" t="s">
         <v>34</v>
       </c>
@@ -21615,7 +22594,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="14.25" thickTop="1">
+    <row r="13" spans="2:14" ht="13.5" thickTop="1">
       <c r="B13" s="111">
         <v>1</v>
       </c>
@@ -21626,15 +22605,15 @@
         <v>48</v>
       </c>
       <c r="E13" s="117" t="s">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="F13" s="54" t="str">
         <f t="shared" ref="F13:F37" ca="1" si="0">IF($D13&lt;&gt;"","u4_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"Srcchk","")</f>
         <v>u4_s_AlertB_avasSrcchk</v>
       </c>
       <c r="G13" s="54" t="str">
-        <f t="shared" ref="G13:G37" ca="1" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
-        <v>vd_s_AlertB_avasRwTx</v>
+        <f t="shared" ref="G13:G37" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
+        <v>NULL</v>
       </c>
       <c r="H13" s="115" t="str">
         <f ca="1">IF($D13&lt;&gt;"","ALERT_CH_"&amp;UPPER($D$6)&amp;IF($D$7=1,"","_"&amp;UPPER($C13)),"")</f>
@@ -22468,7 +23447,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="14.25" thickBot="1">
+    <row r="37" spans="2:14" ht="13.5" thickBot="1">
       <c r="B37" s="102">
         <v>25</v>
       </c>
@@ -22567,21 +23546,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.5" customWidth="1"/>
-    <col min="6" max="6" width="52.875" customWidth="1"/>
-    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.875" customWidth="1"/>
-    <col min="16" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="44.625" customWidth="1"/>
-    <col min="18" max="18" width="73.625" customWidth="1"/>
+    <col min="5" max="5" width="36.453125" customWidth="1"/>
+    <col min="6" max="6" width="52.90625" customWidth="1"/>
+    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.90625" customWidth="1"/>
+    <col min="16" max="16" width="9.90625" customWidth="1"/>
+    <col min="17" max="17" width="44.6328125" customWidth="1"/>
+    <col min="18" max="18" width="73.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="14.25" thickBot="1">
+    <row r="2" spans="2:18" ht="13.5" thickBot="1">
       <c r="B2" t="s">
         <v>196</v>
       </c>
@@ -22589,7 +23568,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="14.25" thickBot="1">
+    <row r="3" spans="2:18" ht="13.5" thickBot="1">
       <c r="B3" s="148" t="s">
         <v>34</v>
       </c>
@@ -22627,7 +23606,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B4" s="179">
         <v>0</v>
       </c>
@@ -22655,7 +23634,7 @@
       </c>
       <c r="R4" s="147"/>
     </row>
-    <row r="5" spans="2:18" ht="14.25" thickTop="1">
+    <row r="5" spans="2:18" ht="13.5" thickTop="1">
       <c r="B5" s="182">
         <v>1</v>
       </c>
@@ -23183,7 +24162,7 @@
       <c r="Q28" s="152"/>
       <c r="R28" s="121"/>
     </row>
-    <row r="29" spans="2:18" ht="14.25" thickBot="1">
+    <row r="29" spans="2:18" ht="13.5" thickBot="1">
       <c r="B29" s="183">
         <v>25</v>
       </c>
@@ -23205,7 +24184,7 @@
       <c r="Q29" s="150"/>
       <c r="R29" s="123"/>
     </row>
-    <row r="32" spans="2:18" ht="14.25" thickBot="1">
+    <row r="32" spans="2:18" ht="13.5" thickBot="1">
       <c r="B32" t="s">
         <v>197</v>
       </c>
@@ -23213,7 +24192,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="14.25" thickBot="1">
+    <row r="33" spans="2:18" ht="13.5" thickBot="1">
       <c r="B33" s="148" t="s">
         <v>34</v>
       </c>
@@ -23245,7 +24224,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B34" s="179">
         <v>0</v>
       </c>
@@ -23271,7 +24250,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="14.25" thickTop="1">
+    <row r="35" spans="2:18" ht="13.5" thickTop="1">
       <c r="B35" s="182">
         <v>1</v>
       </c>
@@ -23799,7 +24778,7 @@
       <c r="Q58" s="152"/>
       <c r="R58" s="184"/>
     </row>
-    <row r="59" spans="2:18" ht="14.25" thickBot="1">
+    <row r="59" spans="2:18" ht="13.5" thickBot="1">
       <c r="B59" s="183">
         <v>25</v>
       </c>
@@ -23850,29 +24829,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="28.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="19.875" customWidth="1"/>
-    <col min="7" max="7" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" customWidth="1"/>
+    <col min="6" max="6" width="19.90625" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
-    <col min="10" max="10" width="28.5" customWidth="1"/>
-    <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="16.125" customWidth="1"/>
-    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.36328125" customWidth="1"/>
+    <col min="10" max="10" width="28.453125" customWidth="1"/>
+    <col min="11" max="11" width="12.36328125" customWidth="1"/>
+    <col min="12" max="12" width="16.08984375" customWidth="1"/>
+    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.25" thickBot="1">
+    <row r="1" spans="2:21" ht="13.5" thickBot="1">
       <c r="C1" s="95" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="14.25" thickBot="1">
+    <row r="2" spans="2:21" ht="13.5" thickBot="1">
       <c r="B2" s="103" t="s">
         <v>58</v>
       </c>
@@ -23916,7 +24895,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="24"/>
       <c r="C3" s="53" t="s">
         <v>110</v>
@@ -23937,12 +24916,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="14.25" thickTop="1">
+    <row r="4" spans="2:21" ht="13.5" thickTop="1">
       <c r="B4" s="24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C4" s="112" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D4" s="119">
         <v>0</v>
@@ -23951,7 +24930,7 @@
         <v>132</v>
       </c>
       <c r="F4" s="198" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G4" s="197" t="s">
         <v>132</v>
@@ -23963,13 +24942,13 @@
         <v>132</v>
       </c>
       <c r="J4" s="199" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K4" s="197" t="s">
         <v>132</v>
       </c>
       <c r="L4" s="198" t="s">
-        <v>221</v>
+        <v>31</v>
       </c>
       <c r="M4" s="54">
         <f ca="1">LEN(N4)</f>
@@ -23989,10 +24968,10 @@
     </row>
     <row r="5" spans="2:21">
       <c r="B5" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="113" t="s">
         <v>217</v>
-      </c>
-      <c r="C5" s="113" t="s">
-        <v>218</v>
       </c>
       <c r="D5" s="120">
         <v>1</v>
@@ -24001,25 +24980,25 @@
         <v>132</v>
       </c>
       <c r="F5" s="199" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G5" s="114" t="s">
         <v>132</v>
       </c>
       <c r="H5" s="199" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I5" s="114" t="s">
         <v>132</v>
       </c>
       <c r="J5" s="199" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K5" s="114" t="s">
         <v>132</v>
       </c>
       <c r="L5" s="199" t="s">
-        <v>221</v>
+        <v>31</v>
       </c>
       <c r="M5" s="49">
         <f t="shared" ref="M5:M68" ca="1" si="1">LEN(N5)</f>
@@ -24039,37 +25018,37 @@
     </row>
     <row r="6" spans="2:21">
       <c r="B6" s="24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C6" s="112" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D6" s="124">
         <v>2</v>
       </c>
       <c r="E6" s="114" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F6" s="199" t="s">
         <v>167</v>
       </c>
       <c r="G6" s="114" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H6" s="199" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I6" s="114" t="s">
         <v>171</v>
       </c>
       <c r="J6" s="199" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K6" s="114" t="s">
         <v>171</v>
       </c>
       <c r="L6" s="199" t="s">
-        <v>221</v>
+        <v>31</v>
       </c>
       <c r="M6" s="49">
         <f t="shared" ca="1" si="1"/>
@@ -24249,7 +25228,7 @@
       </c>
       <c r="U12" s="30"/>
     </row>
-    <row r="13" spans="2:21" ht="14.25" thickBot="1">
+    <row r="13" spans="2:21" ht="13.5" thickBot="1">
       <c r="B13" s="24"/>
       <c r="C13" s="23"/>
       <c r="D13" s="120"/>
@@ -26500,7 +27479,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="14.25" thickBot="1">
+    <row r="103" spans="2:15" ht="13.5" thickBot="1">
       <c r="B103" s="55"/>
       <c r="C103" s="56"/>
       <c r="D103" s="122"/>
@@ -26536,7 +27515,7 @@
       <formula>32</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 G3 I3 E3" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"あり,なし"</formula1>
     </dataValidation>
@@ -26548,7 +27527,7 @@
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000001000000}">
           <x14:formula1>
             <xm:f>Matrix!$H$13:$H$37</xm:f>
@@ -26573,18 +27552,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.125" customWidth="1"/>
+    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.08984375" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.125" customWidth="1"/>
-    <col min="48" max="48" width="23.625" customWidth="1"/>
+    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.08984375" customWidth="1"/>
+    <col min="48" max="48" width="23.6328125" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26600,7 +27579,7 @@
       <c r="B2" s="130" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="298" t="s">
+      <c r="C2" s="303" t="s">
         <v>84</v>
       </c>
       <c r="D2" s="60">
@@ -26699,7 +27678,7 @@
       <c r="AI2" s="60">
         <v>0</v>
       </c>
-      <c r="AJ2" s="300" t="s">
+      <c r="AJ2" s="305" t="s">
         <v>161</v>
       </c>
     </row>
@@ -26707,7 +27686,7 @@
       <c r="B3" s="137" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="299"/>
+      <c r="C3" s="304"/>
       <c r="D3" s="132" t="s">
         <v>61</v>
       </c>
@@ -26796,24 +27775,24 @@
         <v>62</v>
       </c>
       <c r="AG3" s="196" t="s">
+        <v>225</v>
+      </c>
+      <c r="AH3" s="200" t="s">
+        <v>226</v>
+      </c>
+      <c r="AI3" s="200" t="s">
         <v>227</v>
       </c>
-      <c r="AH3" s="200" t="s">
-        <v>228</v>
-      </c>
-      <c r="AI3" s="200" t="s">
-        <v>229</v>
-      </c>
-      <c r="AJ3" s="301"/>
+      <c r="AJ3" s="306"/>
       <c r="AR3" s="96" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A4" s="302" t="s">
+    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A4" s="307" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="303"/>
+      <c r="B4" s="308"/>
       <c r="C4" s="143"/>
       <c r="D4" s="143"/>
       <c r="E4" s="143"/>
@@ -26857,9 +27836,9 @@
       <c r="AV4" s="85"/>
       <c r="AW4" s="86"/>
     </row>
-    <row r="5" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A5" s="304"/>
-      <c r="B5" s="305"/>
+    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A5" s="309"/>
+      <c r="B5" s="310"/>
       <c r="C5" s="144"/>
       <c r="D5" s="144"/>
       <c r="E5" s="144"/>
@@ -27154,7 +28133,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AL7" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27287,7 +28266,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL8" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27307,7 +28286,7 @@
       </c>
       <c r="AU8" s="65" t="str">
         <f ca="1">IF($AW$15&lt;&gt;"NULL","        &amp;"&amp;$AW$15&amp;","&amp;REPT(" ",69-LEN($AW$15))&amp;"/* fp_vd_XDST                                         */","        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */")</f>
-        <v xml:space="preserve">        &amp;vd_s_AlertB_avasRwTx,                                                 /* fp_vd_XDST                                         */</v>
+        <v xml:space="preserve">        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */</v>
       </c>
       <c r="AV8" s="51" t="s">
         <v>72</v>
@@ -27420,7 +28399,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AL9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -28235,7 +29214,7 @@
       </c>
       <c r="AW15" s="70" t="str">
         <f ca="1">IF(AW6&lt;&gt;AW17,VLOOKUP(AW6,Matrix!$C$13:$G$37,5,FALSE),Matrix!G13)</f>
-        <v>vd_s_AlertB_avasRwTx</v>
+        <v>NULL</v>
       </c>
     </row>
     <row r="16" spans="1:49">
@@ -28368,7 +29347,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="14.25" thickBot="1">
+    <row r="17" spans="2:49" ht="13.5" thickBot="1">
       <c r="B17" s="140"/>
       <c r="C17" s="49">
         <f t="shared" si="2"/>
@@ -34738,7 +35717,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="14.25" thickBot="1">
+    <row r="70" spans="1:46" ht="13.5" thickBot="1">
       <c r="A70" s="58" t="s">
         <v>64</v>
       </c>
@@ -55342,7 +56321,7 @@
       <formula>$B$3="Index Table"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Search Table, Index Table"</formula1>
     </dataValidation>
@@ -55354,7 +56333,7 @@
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000001000000}">
           <x14:formula1>
             <xm:f>CH_Design!$C$3:$C$103</xm:f>
@@ -55371,23 +56350,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:CN125"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="80.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="3.375" customWidth="1"/>
+    <col min="2" max="2" width="80.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="3.36328125" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="10.875" customWidth="1"/>
-    <col min="18" max="18" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="10.90625" customWidth="1"/>
+    <col min="18" max="18" width="11.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:92" ht="15" thickBot="1">
+    <row r="2" spans="2:92" ht="14.5" thickBot="1">
       <c r="B2" s="25" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="X2" s="194" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y2" s="194"/>
       <c r="Z2" s="194"/>
@@ -55449,20 +56428,20 @@
       <c r="CM2" s="227"/>
       <c r="CN2" s="227"/>
     </row>
-    <row r="3" spans="2:92" ht="15" thickBot="1">
+    <row r="3" spans="2:92" ht="14.5" thickBot="1">
       <c r="B3" s="100" t="s">
-        <v>255</v>
-      </c>
-      <c r="C3" s="310" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="315" t="s">
         <v>205</v>
       </c>
-      <c r="D3" s="311"/>
-      <c r="E3" s="311"/>
-      <c r="F3" s="311"/>
-      <c r="G3" s="311"/>
-      <c r="H3" s="311"/>
-      <c r="I3" s="311"/>
-      <c r="J3" s="312"/>
+      <c r="D3" s="316"/>
+      <c r="E3" s="316"/>
+      <c r="F3" s="316"/>
+      <c r="G3" s="316"/>
+      <c r="H3" s="316"/>
+      <c r="I3" s="316"/>
+      <c r="J3" s="317"/>
       <c r="K3" s="175"/>
       <c r="L3" s="175"/>
       <c r="M3" s="175"/>
@@ -55475,7 +56454,7 @@
     <row r="4" spans="2:92">
       <c r="B4" s="72"/>
       <c r="C4" s="33" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D4" s="33"/>
       <c r="E4" s="33"/>
@@ -55488,7 +56467,7 @@
       <c r="L4" s="33"/>
       <c r="M4" s="34"/>
       <c r="N4" s="29" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O4" s="45" t="s">
         <v>20</v>
@@ -55501,23 +56480,23 @@
       <c r="B5" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="306" t="s">
-        <v>232</v>
-      </c>
-      <c r="D5" s="307"/>
-      <c r="E5" s="307"/>
-      <c r="F5" s="307"/>
-      <c r="G5" s="307"/>
-      <c r="H5" s="307"/>
-      <c r="I5" s="307"/>
-      <c r="J5" s="308"/>
+      <c r="C5" s="311" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" s="312"/>
+      <c r="E5" s="312"/>
+      <c r="F5" s="312"/>
+      <c r="G5" s="312"/>
+      <c r="H5" s="312"/>
+      <c r="I5" s="312"/>
+      <c r="J5" s="313"/>
       <c r="K5" s="36" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="201"/>
       <c r="M5" s="77"/>
       <c r="N5" s="30" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O5" s="27" t="s">
         <v>23</v>
@@ -55532,120 +56511,120 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:92" ht="27">
+    <row r="6" spans="2:92" ht="26">
       <c r="B6" s="73" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="170" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D6" s="170" t="s">
+        <v>231</v>
+      </c>
+      <c r="E6" s="170" t="s">
+        <v>231</v>
+      </c>
+      <c r="F6" s="170" t="s">
+        <v>232</v>
+      </c>
+      <c r="G6" s="170" t="s">
+        <v>232</v>
+      </c>
+      <c r="H6" s="170" t="s">
+        <v>232</v>
+      </c>
+      <c r="I6" s="170" t="s">
+        <v>232</v>
+      </c>
+      <c r="J6" s="170" t="s">
+        <v>232</v>
+      </c>
+      <c r="K6" s="145" t="s">
         <v>233</v>
       </c>
-      <c r="E6" s="170" t="s">
+      <c r="L6" s="146" t="s">
         <v>233</v>
       </c>
-      <c r="F6" s="170" t="s">
+      <c r="M6" s="203" t="s">
+        <v>233</v>
+      </c>
+      <c r="N6" s="204" t="s">
         <v>234</v>
-      </c>
-      <c r="G6" s="170" t="s">
-        <v>234</v>
-      </c>
-      <c r="H6" s="170" t="s">
-        <v>234</v>
-      </c>
-      <c r="I6" s="170" t="s">
-        <v>234</v>
-      </c>
-      <c r="J6" s="170" t="s">
-        <v>234</v>
-      </c>
-      <c r="K6" s="145" t="s">
-        <v>235</v>
-      </c>
-      <c r="L6" s="146" t="s">
-        <v>235</v>
-      </c>
-      <c r="M6" s="203" t="s">
-        <v>235</v>
-      </c>
-      <c r="N6" s="204" t="s">
-        <v>236</v>
       </c>
       <c r="O6" s="42"/>
       <c r="P6" s="205"/>
       <c r="Q6" s="81"/>
       <c r="R6" s="206" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
-    <row r="7" spans="2:92" ht="27">
+    <row r="7" spans="2:92" ht="26">
       <c r="B7" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="309" t="s">
-        <v>257</v>
-      </c>
-      <c r="D7" s="307"/>
-      <c r="E7" s="307"/>
-      <c r="F7" s="307"/>
-      <c r="G7" s="307"/>
-      <c r="H7" s="307"/>
-      <c r="I7" s="307"/>
-      <c r="J7" s="308"/>
+      <c r="C7" s="314" t="s">
+        <v>255</v>
+      </c>
+      <c r="D7" s="312"/>
+      <c r="E7" s="312"/>
+      <c r="F7" s="312"/>
+      <c r="G7" s="312"/>
+      <c r="H7" s="312"/>
+      <c r="I7" s="312"/>
+      <c r="J7" s="313"/>
       <c r="K7" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L7" s="26" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M7" s="78" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="N7" s="31"/>
       <c r="O7" s="42"/>
       <c r="P7" s="205"/>
       <c r="Q7" s="81"/>
       <c r="R7" s="193" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
-    <row r="8" spans="2:92" ht="136.5">
+    <row r="8" spans="2:92" ht="131">
       <c r="B8" s="73" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="171" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D8" s="171" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="171" t="s">
+        <v>258</v>
+      </c>
+      <c r="F8" s="171" t="s">
+        <v>259</v>
+      </c>
+      <c r="G8" s="171" t="s">
         <v>260</v>
       </c>
-      <c r="F8" s="171" t="s">
+      <c r="H8" s="171" t="s">
         <v>261</v>
       </c>
-      <c r="G8" s="171" t="s">
+      <c r="I8" s="171" t="s">
         <v>262</v>
       </c>
-      <c r="H8" s="171" t="s">
+      <c r="J8" s="171" t="s">
         <v>263</v>
       </c>
-      <c r="I8" s="171" t="s">
+      <c r="K8" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="J8" s="171" t="s">
+      <c r="L8" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="M8" s="78" t="s">
         <v>266</v>
-      </c>
-      <c r="L8" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="M8" s="78" t="s">
-        <v>268</v>
       </c>
       <c r="N8" s="30" t="s">
         <v>29</v>
@@ -55654,63 +56633,63 @@
       <c r="P8" s="205"/>
       <c r="Q8" s="81"/>
       <c r="R8" s="206" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
-    <row r="9" spans="2:92" ht="68.25" thickBot="1">
+    <row r="9" spans="2:92" ht="65.5" thickBot="1">
       <c r="B9" s="75" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="172" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" s="172" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" s="172" t="s">
+        <v>236</v>
+      </c>
+      <c r="F9" s="172" t="s">
+        <v>236</v>
+      </c>
+      <c r="G9" s="172" t="s">
+        <v>236</v>
+      </c>
+      <c r="H9" s="172" t="s">
+        <v>236</v>
+      </c>
+      <c r="I9" s="172" t="s">
+        <v>236</v>
+      </c>
+      <c r="J9" s="172" t="s">
+        <v>236</v>
+      </c>
+      <c r="K9" s="207" t="s">
+        <v>237</v>
+      </c>
+      <c r="L9" s="207" t="s">
         <v>238</v>
       </c>
-      <c r="D9" s="172" t="s">
-        <v>234</v>
-      </c>
-      <c r="E9" s="172" t="s">
+      <c r="M9" s="208" t="s">
         <v>238</v>
       </c>
-      <c r="F9" s="172" t="s">
-        <v>238</v>
-      </c>
-      <c r="G9" s="172" t="s">
-        <v>238</v>
-      </c>
-      <c r="H9" s="172" t="s">
-        <v>238</v>
-      </c>
-      <c r="I9" s="172" t="s">
-        <v>238</v>
-      </c>
-      <c r="J9" s="172" t="s">
-        <v>238</v>
-      </c>
-      <c r="K9" s="207" t="s">
+      <c r="N9" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="O9" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="L9" s="207" t="s">
-        <v>240</v>
-      </c>
-      <c r="M9" s="208" t="s">
-        <v>240</v>
-      </c>
-      <c r="N9" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="O9" s="28" t="s">
-        <v>241</v>
-      </c>
       <c r="P9" s="209" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Q9" s="79"/>
       <c r="R9" s="210" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
-    <row r="10" spans="2:92" ht="14.25" thickTop="1">
+    <row r="10" spans="2:92" ht="13.5" thickTop="1">
       <c r="B10" s="76" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C10" s="173" t="s">
         <v>168</v>
@@ -55737,31 +56716,31 @@
         <v>168</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L10" s="38" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M10" s="211" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N10" s="39" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O10" s="212" t="s">
         <v>31</v>
       </c>
       <c r="P10" s="134" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q10" s="43"/>
       <c r="R10" s="213" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="2:92">
       <c r="B11" s="21" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C11" s="174" t="s">
         <v>168</v>
@@ -55788,31 +56767,31 @@
         <v>168</v>
       </c>
       <c r="K11" s="195" t="s">
+        <v>241</v>
+      </c>
+      <c r="L11" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="M11" s="214" t="s">
         <v>243</v>
       </c>
-      <c r="L11" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="M11" s="214" t="s">
+      <c r="N11" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="O11" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="P11" s="63" t="s">
         <v>245</v>
-      </c>
-      <c r="N11" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="O11" s="41" t="s">
-        <v>234</v>
-      </c>
-      <c r="P11" s="63" t="s">
-        <v>247</v>
       </c>
       <c r="Q11" s="44"/>
       <c r="R11" s="215" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="2:92">
       <c r="B12" s="21" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C12" s="174" t="s">
         <v>168</v>
@@ -55839,31 +56818,31 @@
         <v>168</v>
       </c>
       <c r="K12" s="195" t="s">
+        <v>241</v>
+      </c>
+      <c r="L12" s="35" t="s">
         <v>243</v>
       </c>
-      <c r="L12" s="35" t="s">
-        <v>245</v>
-      </c>
       <c r="M12" s="214" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N12" s="40" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O12" s="216" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="P12" s="63" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q12" s="44"/>
       <c r="R12" s="215" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="2:92">
       <c r="B13" s="21" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C13" s="174" t="s">
         <v>168</v>
@@ -55890,31 +56869,31 @@
         <v>168</v>
       </c>
       <c r="K13" s="195" t="s">
+        <v>241</v>
+      </c>
+      <c r="L13" s="35" t="s">
         <v>243</v>
       </c>
-      <c r="L13" s="35" t="s">
+      <c r="M13" s="214" t="s">
+        <v>243</v>
+      </c>
+      <c r="N13" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="O13" s="216" t="s">
+        <v>249</v>
+      </c>
+      <c r="P13" s="63" t="s">
         <v>245</v>
-      </c>
-      <c r="M13" s="214" t="s">
-        <v>245</v>
-      </c>
-      <c r="N13" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="O13" s="216" t="s">
-        <v>251</v>
-      </c>
-      <c r="P13" s="63" t="s">
-        <v>247</v>
       </c>
       <c r="Q13" s="44"/>
       <c r="R13" s="215" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="2:92">
       <c r="B14" s="21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C14" s="174" t="s">
         <v>168</v>
@@ -55941,31 +56920,31 @@
         <v>168</v>
       </c>
       <c r="K14" s="195" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L14" s="35" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M14" s="214" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N14" s="40" t="s">
         <v>32</v>
       </c>
       <c r="O14" s="41" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P14" s="63" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q14" s="44"/>
       <c r="R14" s="215" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:92" ht="14.25" thickBot="1">
+    <row r="15" spans="2:92" ht="13.5" thickBot="1">
       <c r="B15" s="217" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C15" s="218" t="s">
         <v>168</v>
@@ -55992,22 +56971,22 @@
         <v>168</v>
       </c>
       <c r="K15" s="219" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L15" s="220" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M15" s="221" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N15" s="222" t="s">
         <v>32</v>
       </c>
       <c r="O15" s="223" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P15" s="224" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q15" s="225"/>
       <c r="R15" s="226" t="s">
@@ -56016,7 +56995,7 @@
     </row>
     <row r="78" spans="24:53">
       <c r="X78" s="194" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y78" s="194"/>
       <c r="Z78" s="194"/>
@@ -56086,7 +57065,7 @@
     </row>
     <row r="125" spans="24:57">
       <c r="X125" s="228" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y125" s="194"/>
       <c r="Z125" s="194"/>
@@ -56143,14 +57122,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.125" customWidth="1"/>
+    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="14.25" thickBot="1">
+    <row r="2" spans="2:4" ht="13.5" thickBot="1">
       <c r="B2" s="88" t="s">
         <v>87</v>
       </c>
@@ -56160,7 +57139,7 @@
       </c>
       <c r="D2" s="89"/>
     </row>
-    <row r="3" spans="2:4" ht="14.25" thickBot="1">
+    <row r="3" spans="2:4" ht="13.5" thickBot="1">
       <c r="B3" s="82" t="s">
         <v>85</v>
       </c>
@@ -56171,7 +57150,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="14.25" thickTop="1">
+    <row r="4" spans="2:4" ht="13.5" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -56182,7 +57161,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="40.5">
+    <row r="5" spans="2:4" ht="39">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -56193,7 +57172,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="27">
+    <row r="6" spans="2:4" ht="26">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -56204,7 +57183,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="54">
+    <row r="7" spans="2:4" ht="52">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -56215,7 +57194,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="81">
+    <row r="8" spans="2:4" ht="78">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -56237,7 +57216,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="27">
+    <row r="10" spans="2:4" ht="26">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -56248,7 +57227,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="27">
+    <row r="11" spans="2:4" ht="26">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -56259,7 +57238,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="27">
+    <row r="12" spans="2:4" ht="26">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -56270,7 +57249,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="27">
+    <row r="13" spans="2:4" ht="26">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -56281,7 +57260,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="27">
+    <row r="14" spans="2:4" ht="26">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -56292,7 +57271,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="135">
+    <row r="15" spans="2:4" ht="130">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -56314,7 +57293,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="27">
+    <row r="17" spans="2:4" ht="26">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -56325,7 +57304,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="67.5">
+    <row r="18" spans="2:4" ht="91">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -56336,7 +57315,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="40.5">
+    <row r="19" spans="2:4" ht="39">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -56394,7 +57373,7 @@
       <c r="C26" s="92"/>
       <c r="D26" s="78"/>
     </row>
-    <row r="27" spans="2:4" ht="14.25" thickBot="1">
+    <row r="27" spans="2:4" ht="13.5" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="93"/>
       <c r="D27" s="5"/>

--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_AVAS-CSTD-0-00-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_AVAS-CSTD-0-00-A-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\ソフトチーム\20260106_REMWAR_RW\045\IpcApplication\Vom\Alert\matrix\scc\ref更新\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8F17E7-B50B-4E9D-A1EF-A1F9E4EAB174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333B506C-DCAE-4822-AF6A-0359234B7B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14535" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="22740" windowHeight="14070" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="12" r:id="rId1"/>
@@ -674,7 +674,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2567" uniqueCount="307">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -3247,6 +3247,25 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>1.1.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RWの削除
+[Reference]シート
+RW記載を対象外に変更</t>
+    <rPh sb="23" eb="25">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>タイショウガイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -4691,7 +4710,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="318">
+  <cellXfs count="322">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5443,19 +5462,31 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="81" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10084,6 +10115,370 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88709EDE-F17A-4D3D-8BD2-FFA7E28BAD4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18316575" y="895350"/>
+          <a:ext cx="904875" cy="4333875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33437471-77E4-446F-A7E2-D1E475A256F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19221450" y="171450"/>
+          <a:ext cx="2838450" cy="1171575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>72</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72BB80C9-AED6-4B13-8E88-8537059E704A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22642285" y="24533679"/>
+          <a:ext cx="34004251" cy="4762500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>60</xdr:col>
+      <xdr:colOff>680356</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4167F0A-9DE5-4391-81B7-493198796DDE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="41692285" y="23553964"/>
+          <a:ext cx="6803571" cy="979715"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -21260,10 +21655,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="52" width="2.08984375" style="235" customWidth="1"/>
-    <col min="53" max="16384" width="8.08984375" style="235"/>
+    <col min="1" max="52" width="2.125" style="235" customWidth="1"/>
+    <col min="53" max="16384" width="8.125" style="235"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -21326,27 +21721,27 @@
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="258" t="s">
+      <c r="Y35" s="262" t="s">
         <v>286</v>
       </c>
-      <c r="Z35" s="259"/>
-      <c r="AA35" s="259"/>
-      <c r="AB35" s="259"/>
-      <c r="AC35" s="260"/>
-      <c r="AD35" s="258" t="s">
+      <c r="Z35" s="263"/>
+      <c r="AA35" s="263"/>
+      <c r="AB35" s="263"/>
+      <c r="AC35" s="264"/>
+      <c r="AD35" s="262" t="s">
         <v>287</v>
       </c>
-      <c r="AE35" s="259"/>
-      <c r="AF35" s="259"/>
-      <c r="AG35" s="259"/>
-      <c r="AH35" s="260"/>
-      <c r="AI35" s="258" t="s">
+      <c r="AE35" s="263"/>
+      <c r="AF35" s="263"/>
+      <c r="AG35" s="263"/>
+      <c r="AH35" s="264"/>
+      <c r="AI35" s="262" t="s">
         <v>288</v>
       </c>
-      <c r="AJ35" s="259"/>
-      <c r="AK35" s="259"/>
-      <c r="AL35" s="259"/>
-      <c r="AM35" s="260"/>
+      <c r="AJ35" s="263"/>
+      <c r="AK35" s="263"/>
+      <c r="AL35" s="263"/>
+      <c r="AM35" s="264"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
       <c r="D36" s="239"/>
@@ -21445,27 +21840,27 @@
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="258" t="s">
+      <c r="Y43" s="262" t="s">
         <v>286</v>
       </c>
-      <c r="Z43" s="259"/>
-      <c r="AA43" s="259"/>
-      <c r="AB43" s="259"/>
-      <c r="AC43" s="260"/>
-      <c r="AD43" s="258" t="s">
+      <c r="Z43" s="263"/>
+      <c r="AA43" s="263"/>
+      <c r="AB43" s="263"/>
+      <c r="AC43" s="264"/>
+      <c r="AD43" s="262" t="s">
         <v>287</v>
       </c>
-      <c r="AE43" s="259"/>
-      <c r="AF43" s="259"/>
-      <c r="AG43" s="259"/>
-      <c r="AH43" s="260"/>
-      <c r="AI43" s="258" t="s">
+      <c r="AE43" s="263"/>
+      <c r="AF43" s="263"/>
+      <c r="AG43" s="263"/>
+      <c r="AH43" s="264"/>
+      <c r="AI43" s="262" t="s">
         <v>288</v>
       </c>
-      <c r="AJ43" s="259"/>
-      <c r="AK43" s="259"/>
-      <c r="AL43" s="259"/>
-      <c r="AM43" s="260"/>
+      <c r="AJ43" s="263"/>
+      <c r="AK43" s="263"/>
+      <c r="AL43" s="263"/>
+      <c r="AM43" s="264"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
       <c r="D44" s="239"/>
@@ -21563,27 +21958,27 @@
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="258" t="s">
+      <c r="Y51" s="262" t="s">
         <v>286</v>
       </c>
-      <c r="Z51" s="259"/>
-      <c r="AA51" s="259"/>
-      <c r="AB51" s="259"/>
-      <c r="AC51" s="260"/>
-      <c r="AD51" s="258" t="s">
+      <c r="Z51" s="263"/>
+      <c r="AA51" s="263"/>
+      <c r="AB51" s="263"/>
+      <c r="AC51" s="264"/>
+      <c r="AD51" s="262" t="s">
         <v>287</v>
       </c>
-      <c r="AE51" s="259"/>
-      <c r="AF51" s="259"/>
-      <c r="AG51" s="259"/>
-      <c r="AH51" s="260"/>
-      <c r="AI51" s="258" t="s">
+      <c r="AE51" s="263"/>
+      <c r="AF51" s="263"/>
+      <c r="AG51" s="263"/>
+      <c r="AH51" s="264"/>
+      <c r="AI51" s="262" t="s">
         <v>288</v>
       </c>
-      <c r="AJ51" s="259"/>
-      <c r="AK51" s="259"/>
-      <c r="AL51" s="259"/>
-      <c r="AM51" s="260"/>
+      <c r="AJ51" s="263"/>
+      <c r="AK51" s="263"/>
+      <c r="AL51" s="263"/>
+      <c r="AM51" s="264"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
       <c r="D52" s="239"/>
@@ -21700,14 +22095,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.453125" customWidth="1"/>
-    <col min="5" max="6" width="12.90625" hidden="1" customWidth="1"/>
-    <col min="7" max="22" width="13.08984375" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.875" hidden="1" customWidth="1"/>
+    <col min="7" max="22" width="13.125" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -21718,18 +22113,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="261" t="s">
+      <c r="I2" s="265" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="261"/>
-      <c r="N2" s="261"/>
-      <c r="O2" s="261"/>
-      <c r="P2" s="261"/>
-      <c r="Q2" s="261"/>
-      <c r="R2" s="261"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="265"/>
+      <c r="M2" s="265"/>
+      <c r="N2" s="265"/>
+      <c r="O2" s="265"/>
+      <c r="P2" s="265"/>
+      <c r="Q2" s="265"/>
+      <c r="R2" s="265"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -21742,25 +22137,25 @@
       <c r="H3" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="I3" s="262" t="s">
+      <c r="I3" s="266" t="s">
         <v>203</v>
       </c>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
-      <c r="M3" s="263"/>
-      <c r="N3" s="263"/>
-      <c r="O3" s="263"/>
-      <c r="P3" s="263"/>
-      <c r="Q3" s="263"/>
-      <c r="R3" s="263"/>
+      <c r="J3" s="267"/>
+      <c r="K3" s="267"/>
+      <c r="L3" s="267"/>
+      <c r="M3" s="267"/>
+      <c r="N3" s="267"/>
+      <c r="O3" s="267"/>
+      <c r="P3" s="267"/>
+      <c r="Q3" s="267"/>
+      <c r="R3" s="267"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="22" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.0.2</v>
+        <v>1.1.0</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -21774,45 +22169,45 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B14)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
+    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="266" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="267"/>
-      <c r="E7" s="268" t="s">
+      <c r="C7" s="270" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="271"/>
+      <c r="E7" s="272" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="268"/>
-      <c r="G7" s="269" t="s">
+      <c r="F7" s="272"/>
+      <c r="G7" s="273" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="269"/>
-      <c r="I7" s="269"/>
-      <c r="J7" s="269"/>
-      <c r="K7" s="269"/>
-      <c r="L7" s="269"/>
-      <c r="M7" s="270" t="s">
+      <c r="H7" s="273"/>
+      <c r="I7" s="273"/>
+      <c r="J7" s="273"/>
+      <c r="K7" s="273"/>
+      <c r="L7" s="273"/>
+      <c r="M7" s="274" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="270"/>
-      <c r="O7" s="270"/>
-      <c r="P7" s="270"/>
-      <c r="Q7" s="270"/>
-      <c r="R7" s="271"/>
-      <c r="S7" s="264" t="s">
+      <c r="N7" s="274"/>
+      <c r="O7" s="274"/>
+      <c r="P7" s="274"/>
+      <c r="Q7" s="274"/>
+      <c r="R7" s="275"/>
+      <c r="S7" s="268" t="s">
         <v>279</v>
       </c>
-      <c r="T7" s="264"/>
-      <c r="U7" s="264"/>
-      <c r="V7" s="264"/>
-      <c r="W7" s="264"/>
-      <c r="X7" s="265"/>
+      <c r="T7" s="268"/>
+      <c r="U7" s="268"/>
+      <c r="V7" s="268"/>
+      <c r="W7" s="268"/>
+      <c r="X7" s="269"/>
     </row>
-    <row r="8" spans="2:24" ht="26.5" thickBot="1">
+    <row r="8" spans="2:24" ht="27.75" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>93</v>
       </c>
@@ -21883,7 +22278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="13.5" thickTop="1">
+    <row r="9" spans="2:24" ht="14.25" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -21955,7 +22350,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="39">
+    <row r="10" spans="2:24" ht="40.5">
       <c r="B10" s="9">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
@@ -22007,7 +22402,7 @@
         <v>45806</v>
       </c>
     </row>
-    <row r="11" spans="2:24" ht="91">
+    <row r="11" spans="2:24" ht="94.5">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -22024,36 +22419,40 @@
       <c r="F11" s="255" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="231"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="231"/>
-      <c r="W11" s="256" t="s">
+      <c r="G11" s="256"/>
+      <c r="H11" s="256"/>
+      <c r="I11" s="256"/>
+      <c r="J11" s="256"/>
+      <c r="K11" s="256"/>
+      <c r="L11" s="256"/>
+      <c r="M11" s="256"/>
+      <c r="N11" s="256"/>
+      <c r="O11" s="256"/>
+      <c r="P11" s="256"/>
+      <c r="Q11" s="256"/>
+      <c r="R11" s="256"/>
+      <c r="S11" s="256"/>
+      <c r="T11" s="257"/>
+      <c r="U11" s="256"/>
+      <c r="V11" s="257"/>
+      <c r="W11" s="258" t="s">
         <v>301</v>
       </c>
-      <c r="X11" s="257">
+      <c r="X11" s="259">
         <v>46008</v>
       </c>
     </row>
-    <row r="12" spans="2:24">
+    <row r="12" spans="2:24" ht="40.5">
       <c r="B12" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="C12" s="261" t="s">
+        <v>305</v>
+      </c>
+      <c r="D12" s="260" t="s">
+        <v>306</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -22075,7 +22474,7 @@
       <c r="W12" s="1"/>
       <c r="X12" s="232"/>
     </row>
-    <row r="13" spans="2:24" ht="13.5" thickBot="1">
+    <row r="13" spans="2:24" ht="14.25" thickBot="1">
       <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -22129,11 +22528,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22147,13 +22546,13 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="14.25" thickBot="1">
       <c r="B6" s="157" t="s">
         <v>135</v>
       </c>
       <c r="C6" s="157"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="14.25" thickBot="1">
       <c r="C7" s="82" t="s">
         <v>137</v>
       </c>
@@ -22173,7 +22572,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="26">
+    <row r="9" spans="2:5" ht="27">
       <c r="C9" s="167">
         <v>1</v>
       </c>
@@ -22184,7 +22583,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="14.25" thickBot="1">
       <c r="C10" s="165"/>
       <c r="D10" s="93"/>
       <c r="E10" s="5"/>
@@ -22192,14 +22591,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="163"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="14.25" thickBot="1">
       <c r="B12" s="158" t="s">
         <v>136</v>
       </c>
       <c r="C12" s="89"/>
       <c r="D12" s="89"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="14.25" thickBot="1">
       <c r="B13" s="159"/>
       <c r="C13" s="164" t="s">
         <v>137</v>
@@ -22211,7 +22610,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="14.25" thickTop="1">
       <c r="C14" s="161">
         <v>0</v>
       </c>
@@ -22288,17 +22687,17 @@
         <v>174</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="14.25" thickBot="1">
       <c r="C21" s="165"/>
       <c r="D21" s="93"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="14.25" thickBot="1">
       <c r="B24" s="157" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="14.25" thickBot="1">
       <c r="C25" s="164" t="s">
         <v>137</v>
       </c>
@@ -22385,26 +22784,26 @@
       <c r="D33" s="92"/>
       <c r="E33" s="78"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="14.25" thickBot="1">
       <c r="C34" s="165"/>
       <c r="D34" s="93"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="14.25" thickBot="1">
       <c r="B37" s="157" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="272"/>
-      <c r="D38" s="273"/>
+      <c r="C38" s="276"/>
+      <c r="D38" s="277"/>
       <c r="E38" s="118" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
-      <c r="C39" s="274"/>
-      <c r="D39" s="275"/>
+    <row r="39" spans="2:5" ht="14.25" thickBot="1">
+      <c r="C39" s="278"/>
+      <c r="D39" s="279"/>
       <c r="E39" s="5" t="s">
         <v>125</v>
       </c>
@@ -22433,133 +22832,133 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.90625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.875" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="301" t="s">
+      <c r="B2" s="305" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="302"/>
-      <c r="D2" s="289" t="s">
+      <c r="C2" s="306"/>
+      <c r="D2" s="293" t="s">
         <v>215</v>
       </c>
-      <c r="E2" s="290"/>
-      <c r="F2" s="290"/>
-      <c r="G2" s="290"/>
-      <c r="H2" s="291"/>
+      <c r="E2" s="294"/>
+      <c r="F2" s="294"/>
+      <c r="G2" s="294"/>
+      <c r="H2" s="295"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="276" t="s">
+      <c r="B3" s="280" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="277"/>
-      <c r="D3" s="292" t="s">
+      <c r="C3" s="281"/>
+      <c r="D3" s="296" t="s">
         <v>209</v>
       </c>
-      <c r="E3" s="293"/>
-      <c r="F3" s="293"/>
-      <c r="G3" s="293"/>
-      <c r="H3" s="294"/>
+      <c r="E3" s="297"/>
+      <c r="F3" s="297"/>
+      <c r="G3" s="297"/>
+      <c r="H3" s="298"/>
     </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="287" t="s">
+    <row r="4" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B4" s="291" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="288"/>
-      <c r="D4" s="295" t="str">
+      <c r="C4" s="292"/>
+      <c r="D4" s="299" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_B_AVAS-CSTD-0-00-A-C0.c</v>
       </c>
-      <c r="E4" s="296"/>
-      <c r="F4" s="296"/>
-      <c r="G4" s="296"/>
-      <c r="H4" s="297"/>
+      <c r="E4" s="300"/>
+      <c r="F4" s="300"/>
+      <c r="G4" s="300"/>
+      <c r="H4" s="301"/>
     </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+    <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="301" t="s">
+      <c r="B6" s="305" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="302"/>
-      <c r="D6" s="298" t="str">
+      <c r="C6" s="306"/>
+      <c r="D6" s="302" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>B_AVAS</v>
       </c>
-      <c r="E6" s="299"/>
-      <c r="F6" s="299"/>
-      <c r="G6" s="299"/>
-      <c r="H6" s="300"/>
+      <c r="E6" s="303"/>
+      <c r="F6" s="303"/>
+      <c r="G6" s="303"/>
+      <c r="H6" s="304"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="276" t="s">
+      <c r="B7" s="280" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="277"/>
-      <c r="D7" s="278">
+      <c r="C7" s="281"/>
+      <c r="D7" s="282">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="279"/>
-      <c r="F7" s="279"/>
-      <c r="G7" s="279"/>
-      <c r="H7" s="280"/>
+      <c r="E7" s="283"/>
+      <c r="F7" s="283"/>
+      <c r="G7" s="283"/>
+      <c r="H7" s="284"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="276" t="s">
+      <c r="B8" s="280" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="277"/>
-      <c r="D8" s="278" t="str">
+      <c r="C8" s="281"/>
+      <c r="D8" s="282" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_B_AVAS_MTRX</v>
       </c>
-      <c r="E8" s="279"/>
-      <c r="F8" s="279"/>
-      <c r="G8" s="279"/>
-      <c r="H8" s="280"/>
+      <c r="E8" s="283"/>
+      <c r="F8" s="283"/>
+      <c r="G8" s="283"/>
+      <c r="H8" s="284"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="276" t="s">
+      <c r="B9" s="280" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="277"/>
-      <c r="D9" s="281" t="s">
+      <c r="C9" s="281"/>
+      <c r="D9" s="285" t="s">
         <v>207</v>
       </c>
-      <c r="E9" s="282"/>
-      <c r="F9" s="282"/>
-      <c r="G9" s="282"/>
-      <c r="H9" s="283"/>
+      <c r="E9" s="286"/>
+      <c r="F9" s="286"/>
+      <c r="G9" s="286"/>
+      <c r="H9" s="287"/>
     </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="287" t="s">
+    <row r="10" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B10" s="291" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="288"/>
-      <c r="D10" s="284">
+      <c r="C10" s="292"/>
+      <c r="D10" s="288">
         <v>103</v>
       </c>
-      <c r="E10" s="285"/>
-      <c r="F10" s="285"/>
-      <c r="G10" s="285"/>
-      <c r="H10" s="286"/>
+      <c r="E10" s="289"/>
+      <c r="F10" s="289"/>
+      <c r="G10" s="289"/>
+      <c r="H10" s="290"/>
     </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="12" spans="2:14" ht="14.25" thickBot="1">
       <c r="B12" s="148" t="s">
         <v>34</v>
       </c>
@@ -22594,7 +22993,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="14.25" thickTop="1">
       <c r="B13" s="111">
         <v>1</v>
       </c>
@@ -23447,7 +23846,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="14.25" thickBot="1">
       <c r="B37" s="102">
         <v>25</v>
       </c>
@@ -23546,21 +23945,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="52.90625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.875" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="14.25" thickBot="1">
       <c r="B2" t="s">
         <v>196</v>
       </c>
@@ -23568,7 +23967,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="14.25" thickBot="1">
       <c r="B3" s="148" t="s">
         <v>34</v>
       </c>
@@ -23606,7 +24005,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B4" s="179">
         <v>0</v>
       </c>
@@ -23634,7 +24033,7 @@
       </c>
       <c r="R4" s="147"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="14.25" thickTop="1">
       <c r="B5" s="182">
         <v>1</v>
       </c>
@@ -24162,7 +24561,7 @@
       <c r="Q28" s="152"/>
       <c r="R28" s="121"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="14.25" thickBot="1">
       <c r="B29" s="183">
         <v>25</v>
       </c>
@@ -24184,7 +24583,7 @@
       <c r="Q29" s="150"/>
       <c r="R29" s="123"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="14.25" thickBot="1">
       <c r="B32" t="s">
         <v>197</v>
       </c>
@@ -24192,7 +24591,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="14.25" thickBot="1">
       <c r="B33" s="148" t="s">
         <v>34</v>
       </c>
@@ -24224,7 +24623,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B34" s="179">
         <v>0</v>
       </c>
@@ -24250,7 +24649,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="14.25" thickTop="1">
       <c r="B35" s="182">
         <v>1</v>
       </c>
@@ -24778,7 +25177,7 @@
       <c r="Q58" s="152"/>
       <c r="R58" s="184"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="14.25" thickBot="1">
       <c r="B59" s="183">
         <v>25</v>
       </c>
@@ -24829,29 +25228,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.90625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.875" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" customWidth="1"/>
-    <col min="10" max="10" width="28.453125" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="28.5" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="14.25" thickBot="1">
       <c r="C1" s="95" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="14.25" thickBot="1">
       <c r="B2" s="103" t="s">
         <v>58</v>
       </c>
@@ -24895,7 +25294,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="24"/>
       <c r="C3" s="53" t="s">
         <v>110</v>
@@ -24916,7 +25315,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="24" t="s">
         <v>216</v>
       </c>
@@ -25228,7 +25627,7 @@
       </c>
       <c r="U12" s="30"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="14.25" thickBot="1">
       <c r="B13" s="24"/>
       <c r="C13" s="23"/>
       <c r="D13" s="120"/>
@@ -27479,7 +27878,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="14.25" thickBot="1">
       <c r="B103" s="55"/>
       <c r="C103" s="56"/>
       <c r="D103" s="122"/>
@@ -27552,18 +27951,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -27579,7 +27978,7 @@
       <c r="B2" s="130" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="303" t="s">
+      <c r="C2" s="307" t="s">
         <v>84</v>
       </c>
       <c r="D2" s="60">
@@ -27678,7 +28077,7 @@
       <c r="AI2" s="60">
         <v>0</v>
       </c>
-      <c r="AJ2" s="305" t="s">
+      <c r="AJ2" s="309" t="s">
         <v>161</v>
       </c>
     </row>
@@ -27686,7 +28085,7 @@
       <c r="B3" s="137" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="304"/>
+      <c r="C3" s="308"/>
       <c r="D3" s="132" t="s">
         <v>61</v>
       </c>
@@ -27783,16 +28182,16 @@
       <c r="AI3" s="200" t="s">
         <v>227</v>
       </c>
-      <c r="AJ3" s="306"/>
+      <c r="AJ3" s="310"/>
       <c r="AR3" s="96" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A4" s="307" t="s">
+    <row r="4" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A4" s="311" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="308"/>
+      <c r="B4" s="312"/>
       <c r="C4" s="143"/>
       <c r="D4" s="143"/>
       <c r="E4" s="143"/>
@@ -27836,9 +28235,9 @@
       <c r="AV4" s="85"/>
       <c r="AW4" s="86"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A5" s="309"/>
-      <c r="B5" s="310"/>
+    <row r="5" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A5" s="313"/>
+      <c r="B5" s="314"/>
       <c r="C5" s="144"/>
       <c r="D5" s="144"/>
       <c r="E5" s="144"/>
@@ -29347,7 +29746,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="14.25" thickBot="1">
       <c r="B17" s="140"/>
       <c r="C17" s="49">
         <f t="shared" si="2"/>
@@ -35717,7 +36116,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="14.25" thickBot="1">
       <c r="A70" s="58" t="s">
         <v>64</v>
       </c>
@@ -56350,18 +56749,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:CN125"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="80.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
+    <col min="2" max="2" width="80.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="10.90625" customWidth="1"/>
-    <col min="18" max="18" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="10.875" customWidth="1"/>
+    <col min="18" max="18" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:92" ht="14.5" thickBot="1">
+    <row r="2" spans="2:92" ht="15" thickBot="1">
       <c r="B2" s="25" t="s">
         <v>274</v>
       </c>
@@ -56428,20 +56827,20 @@
       <c r="CM2" s="227"/>
       <c r="CN2" s="227"/>
     </row>
-    <row r="3" spans="2:92" ht="14.5" thickBot="1">
+    <row r="3" spans="2:92" ht="15" thickBot="1">
       <c r="B3" s="100" t="s">
         <v>253</v>
       </c>
-      <c r="C3" s="315" t="s">
+      <c r="C3" s="319" t="s">
         <v>205</v>
       </c>
-      <c r="D3" s="316"/>
-      <c r="E3" s="316"/>
-      <c r="F3" s="316"/>
-      <c r="G3" s="316"/>
-      <c r="H3" s="316"/>
-      <c r="I3" s="316"/>
-      <c r="J3" s="317"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
+      <c r="I3" s="320"/>
+      <c r="J3" s="321"/>
       <c r="K3" s="175"/>
       <c r="L3" s="175"/>
       <c r="M3" s="175"/>
@@ -56480,16 +56879,16 @@
       <c r="B5" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="311" t="s">
+      <c r="C5" s="315" t="s">
         <v>230</v>
       </c>
-      <c r="D5" s="312"/>
-      <c r="E5" s="312"/>
-      <c r="F5" s="312"/>
-      <c r="G5" s="312"/>
-      <c r="H5" s="312"/>
-      <c r="I5" s="312"/>
-      <c r="J5" s="313"/>
+      <c r="D5" s="316"/>
+      <c r="E5" s="316"/>
+      <c r="F5" s="316"/>
+      <c r="G5" s="316"/>
+      <c r="H5" s="316"/>
+      <c r="I5" s="316"/>
+      <c r="J5" s="317"/>
       <c r="K5" s="36" t="s">
         <v>22</v>
       </c>
@@ -56511,7 +56910,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:92" ht="26">
+    <row r="6" spans="2:92" ht="27">
       <c r="B6" s="73" t="s">
         <v>33</v>
       </c>
@@ -56558,20 +56957,20 @@
         <v>235</v>
       </c>
     </row>
-    <row r="7" spans="2:92" ht="26">
+    <row r="7" spans="2:92" ht="27">
       <c r="B7" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="314" t="s">
+      <c r="C7" s="318" t="s">
         <v>255</v>
       </c>
-      <c r="D7" s="312"/>
-      <c r="E7" s="312"/>
-      <c r="F7" s="312"/>
-      <c r="G7" s="312"/>
-      <c r="H7" s="312"/>
-      <c r="I7" s="312"/>
-      <c r="J7" s="313"/>
+      <c r="D7" s="316"/>
+      <c r="E7" s="316"/>
+      <c r="F7" s="316"/>
+      <c r="G7" s="316"/>
+      <c r="H7" s="316"/>
+      <c r="I7" s="316"/>
+      <c r="J7" s="317"/>
       <c r="K7" s="1" t="s">
         <v>256</v>
       </c>
@@ -56589,7 +56988,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="8" spans="2:92" ht="131">
+    <row r="8" spans="2:92" ht="136.5">
       <c r="B8" s="73" t="s">
         <v>28</v>
       </c>
@@ -56636,7 +57035,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="9" spans="2:92" ht="65.5" thickBot="1">
+    <row r="9" spans="2:92" ht="68.25" thickBot="1">
       <c r="B9" s="75" t="s">
         <v>30</v>
       </c>
@@ -56687,7 +57086,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="2:92" ht="13.5" thickTop="1">
+    <row r="10" spans="2:92" ht="14.25" thickTop="1">
       <c r="B10" s="76" t="s">
         <v>273</v>
       </c>
@@ -56942,7 +57341,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:92" ht="13.5" thickBot="1">
+    <row r="15" spans="2:92" ht="14.25" thickBot="1">
       <c r="B15" s="217" t="s">
         <v>276</v>
       </c>
@@ -57122,14 +57521,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="14.25" thickBot="1">
       <c r="B2" s="88" t="s">
         <v>87</v>
       </c>
@@ -57139,7 +57538,7 @@
       </c>
       <c r="D2" s="89"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="14.25" thickBot="1">
       <c r="B3" s="82" t="s">
         <v>85</v>
       </c>
@@ -57150,7 +57549,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="14.25" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -57161,7 +57560,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="40.5">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -57172,7 +57571,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="27">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -57183,7 +57582,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="54">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -57194,7 +57593,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="81">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -57216,7 +57615,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="27">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -57227,7 +57626,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="27">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -57238,7 +57637,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="27">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -57249,7 +57648,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="27">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -57260,7 +57659,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="27">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -57271,7 +57670,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="135">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -57293,7 +57692,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="27">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -57304,7 +57703,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="67.5">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -57315,7 +57714,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="40.5">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -57373,7 +57772,7 @@
       <c r="C26" s="92"/>
       <c r="D26" s="78"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="14.25" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="93"/>
       <c r="D27" s="5"/>
